--- a/Config/Datas/Tables/d_动画片段_AnimationClipConfig.xlsx
+++ b/Config/Datas/Tables/d_动画片段_AnimationClipConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbAnimationClip" sheetId="1" r:id="Rccee9d9600f94958"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbAnimationClip" sheetId="1" r:id="R57c8daa4333d41fe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -644,13 +644,13 @@
         <x:v>配对纹理资源ID</x:v>
       </x:c>
       <x:c r="E4" s="27" t="str">
-        <x:v>仅确认 fd=站立、pb=移动，其余为 Unknown</x:v>
+        <x:v>按类别分类；Unused 不接入播放</x:v>
       </x:c>
       <x:c r="F4" s="27" t="str">
-        <x:v>原始文件动作后缀，禁止据名称猜测语义</x:v>
+        <x:v>主角 fd 待机；怪物 zd 待机；均 pb 移动</x:v>
       </x:c>
       <x:c r="G4" s="28" t="str">
-        <x:v>站立和移动循环播放</x:v>
+        <x:v>待机和移动循环；施法不中断移动</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -665,7 +665,7 @@
         <x:v>120001</x:v>
       </x:c>
       <x:c r="E5" s="36" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F5" s="36" t="str">
         <x:v>bj</x:v>
@@ -707,7 +707,7 @@
         <x:v>120003</x:v>
       </x:c>
       <x:c r="E7" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F7" s="38" t="str">
         <x:v>gj</x:v>
@@ -749,7 +749,7 @@
         <x:v>120005</x:v>
       </x:c>
       <x:c r="E9" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F9" s="38" t="str">
         <x:v>sf1</x:v>
@@ -770,7 +770,7 @@
         <x:v>120006</x:v>
       </x:c>
       <x:c r="E10" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F10" s="38" t="str">
         <x:v>sf2</x:v>
@@ -791,7 +791,7 @@
         <x:v>120007</x:v>
       </x:c>
       <x:c r="E11" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F11" s="38" t="str">
         <x:v>sf3</x:v>
@@ -812,7 +812,7 @@
         <x:v>120008</x:v>
       </x:c>
       <x:c r="E12" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F12" s="38" t="str">
         <x:v>sw</x:v>
@@ -833,7 +833,7 @@
         <x:v>120009</x:v>
       </x:c>
       <x:c r="E13" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F13" s="38" t="str">
         <x:v>zd</x:v>
@@ -854,7 +854,7 @@
         <x:v>120010</x:v>
       </x:c>
       <x:c r="E14" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F14" s="38" t="str">
         <x:v>bj</x:v>
@@ -896,7 +896,7 @@
         <x:v>120012</x:v>
       </x:c>
       <x:c r="E16" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F16" s="38" t="str">
         <x:v>gj</x:v>
@@ -938,7 +938,7 @@
         <x:v>120014</x:v>
       </x:c>
       <x:c r="E18" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F18" s="38" t="str">
         <x:v>sf1</x:v>
@@ -959,7 +959,7 @@
         <x:v>120015</x:v>
       </x:c>
       <x:c r="E19" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F19" s="38" t="str">
         <x:v>sf2</x:v>
@@ -980,7 +980,7 @@
         <x:v>120016</x:v>
       </x:c>
       <x:c r="E20" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F20" s="38" t="str">
         <x:v>sf3</x:v>
@@ -1001,7 +1001,7 @@
         <x:v>120017</x:v>
       </x:c>
       <x:c r="E21" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F21" s="38" t="str">
         <x:v>sw</x:v>
@@ -1022,7 +1022,7 @@
         <x:v>120018</x:v>
       </x:c>
       <x:c r="E22" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F22" s="38" t="str">
         <x:v>zd</x:v>
@@ -1043,7 +1043,7 @@
         <x:v>120019</x:v>
       </x:c>
       <x:c r="E23" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F23" s="38" t="str">
         <x:v>bj</x:v>
@@ -1085,7 +1085,7 @@
         <x:v>120021</x:v>
       </x:c>
       <x:c r="E25" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F25" s="38" t="str">
         <x:v>gj</x:v>
@@ -1127,7 +1127,7 @@
         <x:v>120023</x:v>
       </x:c>
       <x:c r="E27" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F27" s="38" t="str">
         <x:v>sf1</x:v>
@@ -1148,7 +1148,7 @@
         <x:v>120024</x:v>
       </x:c>
       <x:c r="E28" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F28" s="38" t="str">
         <x:v>sf2</x:v>
@@ -1169,7 +1169,7 @@
         <x:v>120025</x:v>
       </x:c>
       <x:c r="E29" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F29" s="38" t="str">
         <x:v>sf3</x:v>
@@ -1190,7 +1190,7 @@
         <x:v>120026</x:v>
       </x:c>
       <x:c r="E30" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F30" s="38" t="str">
         <x:v>sw</x:v>
@@ -1211,7 +1211,7 @@
         <x:v>120027</x:v>
       </x:c>
       <x:c r="E31" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F31" s="38" t="str">
         <x:v>zd</x:v>
@@ -1232,7 +1232,7 @@
         <x:v>120028</x:v>
       </x:c>
       <x:c r="E32" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F32" s="38" t="str">
         <x:v>bj</x:v>
@@ -1274,7 +1274,7 @@
         <x:v>120030</x:v>
       </x:c>
       <x:c r="E34" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F34" s="38" t="str">
         <x:v>gj</x:v>
@@ -1316,7 +1316,7 @@
         <x:v>120032</x:v>
       </x:c>
       <x:c r="E36" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F36" s="38" t="str">
         <x:v>sf1</x:v>
@@ -1337,7 +1337,7 @@
         <x:v>120033</x:v>
       </x:c>
       <x:c r="E37" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F37" s="38" t="str">
         <x:v>sf2</x:v>
@@ -1358,7 +1358,7 @@
         <x:v>120034</x:v>
       </x:c>
       <x:c r="E38" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F38" s="38" t="str">
         <x:v>sf3</x:v>
@@ -1379,7 +1379,7 @@
         <x:v>120035</x:v>
       </x:c>
       <x:c r="E39" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F39" s="38" t="str">
         <x:v>sw</x:v>
@@ -1400,7 +1400,7 @@
         <x:v>120036</x:v>
       </x:c>
       <x:c r="E40" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F40" s="38" t="str">
         <x:v>zd</x:v>
@@ -1421,7 +1421,7 @@
         <x:v>120037</x:v>
       </x:c>
       <x:c r="E41" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F41" s="38" t="str">
         <x:v>bj</x:v>
@@ -1463,7 +1463,7 @@
         <x:v>120039</x:v>
       </x:c>
       <x:c r="E43" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F43" s="38" t="str">
         <x:v>gj</x:v>
@@ -1505,7 +1505,7 @@
         <x:v>120041</x:v>
       </x:c>
       <x:c r="E45" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F45" s="38" t="str">
         <x:v>sf1</x:v>
@@ -1526,7 +1526,7 @@
         <x:v>120042</x:v>
       </x:c>
       <x:c r="E46" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F46" s="38" t="str">
         <x:v>sf2</x:v>
@@ -1547,7 +1547,7 @@
         <x:v>120043</x:v>
       </x:c>
       <x:c r="E47" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F47" s="38" t="str">
         <x:v>sf3</x:v>
@@ -1568,7 +1568,7 @@
         <x:v>120044</x:v>
       </x:c>
       <x:c r="E48" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F48" s="38" t="str">
         <x:v>sw</x:v>
@@ -1589,7 +1589,7 @@
         <x:v>120045</x:v>
       </x:c>
       <x:c r="E49" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F49" s="38" t="str">
         <x:v>zd</x:v>
@@ -1631,7 +1631,7 @@
         <x:v>120047</x:v>
       </x:c>
       <x:c r="E51" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F51" s="38" t="str">
         <x:v>bj</x:v>
@@ -1673,7 +1673,7 @@
         <x:v>120049</x:v>
       </x:c>
       <x:c r="E53" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F53" s="38" t="str">
         <x:v>gj</x:v>
@@ -1715,7 +1715,7 @@
         <x:v>120051</x:v>
       </x:c>
       <x:c r="E55" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F55" s="38" t="str">
         <x:v>sf1</x:v>
@@ -1736,7 +1736,7 @@
         <x:v>120052</x:v>
       </x:c>
       <x:c r="E56" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F56" s="38" t="str">
         <x:v>sf2</x:v>
@@ -1757,7 +1757,7 @@
         <x:v>120053</x:v>
       </x:c>
       <x:c r="E57" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F57" s="38" t="str">
         <x:v>sf3</x:v>
@@ -1778,7 +1778,7 @@
         <x:v>120054</x:v>
       </x:c>
       <x:c r="E58" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F58" s="38" t="str">
         <x:v>sw</x:v>
@@ -1799,7 +1799,7 @@
         <x:v>120055</x:v>
       </x:c>
       <x:c r="E59" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F59" s="38" t="str">
         <x:v>zd</x:v>
@@ -1820,7 +1820,7 @@
         <x:v>120056</x:v>
       </x:c>
       <x:c r="E60" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F60" s="38" t="str">
         <x:v>bj</x:v>
@@ -1862,7 +1862,7 @@
         <x:v>120058</x:v>
       </x:c>
       <x:c r="E62" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F62" s="38" t="str">
         <x:v>gj</x:v>
@@ -1904,7 +1904,7 @@
         <x:v>120060</x:v>
       </x:c>
       <x:c r="E64" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F64" s="38" t="str">
         <x:v>sf1</x:v>
@@ -1925,7 +1925,7 @@
         <x:v>120061</x:v>
       </x:c>
       <x:c r="E65" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F65" s="38" t="str">
         <x:v>sf2</x:v>
@@ -1946,7 +1946,7 @@
         <x:v>120062</x:v>
       </x:c>
       <x:c r="E66" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F66" s="38" t="str">
         <x:v>sf3</x:v>
@@ -1967,7 +1967,7 @@
         <x:v>120063</x:v>
       </x:c>
       <x:c r="E67" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F67" s="38" t="str">
         <x:v>sw</x:v>
@@ -1988,7 +1988,7 @@
         <x:v>120064</x:v>
       </x:c>
       <x:c r="E68" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F68" s="38" t="str">
         <x:v>zd</x:v>
@@ -2009,7 +2009,7 @@
         <x:v>120065</x:v>
       </x:c>
       <x:c r="E69" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F69" s="38" t="str">
         <x:v>bj</x:v>
@@ -2051,7 +2051,7 @@
         <x:v>120067</x:v>
       </x:c>
       <x:c r="E71" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F71" s="38" t="str">
         <x:v>gj</x:v>
@@ -2093,7 +2093,7 @@
         <x:v>120069</x:v>
       </x:c>
       <x:c r="E73" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F73" s="38" t="str">
         <x:v>sf1</x:v>
@@ -2114,7 +2114,7 @@
         <x:v>120070</x:v>
       </x:c>
       <x:c r="E74" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F74" s="38" t="str">
         <x:v>sf2</x:v>
@@ -2135,7 +2135,7 @@
         <x:v>120071</x:v>
       </x:c>
       <x:c r="E75" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F75" s="38" t="str">
         <x:v>sf3</x:v>
@@ -2156,7 +2156,7 @@
         <x:v>120072</x:v>
       </x:c>
       <x:c r="E76" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F76" s="38" t="str">
         <x:v>sw</x:v>
@@ -2177,7 +2177,7 @@
         <x:v>120073</x:v>
       </x:c>
       <x:c r="E77" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F77" s="38" t="str">
         <x:v>zd</x:v>
@@ -2198,7 +2198,7 @@
         <x:v>120074</x:v>
       </x:c>
       <x:c r="E78" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F78" s="38" t="str">
         <x:v>bj</x:v>
@@ -2240,7 +2240,7 @@
         <x:v>120076</x:v>
       </x:c>
       <x:c r="E80" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F80" s="38" t="str">
         <x:v>gj</x:v>
@@ -2282,7 +2282,7 @@
         <x:v>120078</x:v>
       </x:c>
       <x:c r="E82" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F82" s="38" t="str">
         <x:v>sf1</x:v>
@@ -2303,7 +2303,7 @@
         <x:v>120079</x:v>
       </x:c>
       <x:c r="E83" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F83" s="38" t="str">
         <x:v>sf2</x:v>
@@ -2324,7 +2324,7 @@
         <x:v>120080</x:v>
       </x:c>
       <x:c r="E84" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F84" s="38" t="str">
         <x:v>sf3</x:v>
@@ -2345,7 +2345,7 @@
         <x:v>120081</x:v>
       </x:c>
       <x:c r="E85" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F85" s="38" t="str">
         <x:v>sw</x:v>
@@ -2366,7 +2366,7 @@
         <x:v>120082</x:v>
       </x:c>
       <x:c r="E86" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F86" s="38" t="str">
         <x:v>zd</x:v>
@@ -2387,7 +2387,7 @@
         <x:v>120083</x:v>
       </x:c>
       <x:c r="E87" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F87" s="38" t="str">
         <x:v>bj</x:v>
@@ -2429,7 +2429,7 @@
         <x:v>120085</x:v>
       </x:c>
       <x:c r="E89" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F89" s="38" t="str">
         <x:v>gj</x:v>
@@ -2471,7 +2471,7 @@
         <x:v>120087</x:v>
       </x:c>
       <x:c r="E91" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F91" s="38" t="str">
         <x:v>sf1</x:v>
@@ -2492,7 +2492,7 @@
         <x:v>120088</x:v>
       </x:c>
       <x:c r="E92" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F92" s="38" t="str">
         <x:v>sf2</x:v>
@@ -2513,7 +2513,7 @@
         <x:v>120089</x:v>
       </x:c>
       <x:c r="E93" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F93" s="38" t="str">
         <x:v>sf3</x:v>
@@ -2534,7 +2534,7 @@
         <x:v>120090</x:v>
       </x:c>
       <x:c r="E94" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F94" s="38" t="str">
         <x:v>sw</x:v>
@@ -2555,7 +2555,7 @@
         <x:v>120091</x:v>
       </x:c>
       <x:c r="E95" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F95" s="38" t="str">
         <x:v>zd</x:v>
@@ -2576,7 +2576,7 @@
         <x:v>120092</x:v>
       </x:c>
       <x:c r="E96" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F96" s="38" t="str">
         <x:v>bj</x:v>
@@ -2618,7 +2618,7 @@
         <x:v>120094</x:v>
       </x:c>
       <x:c r="E98" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F98" s="38" t="str">
         <x:v>gj</x:v>
@@ -2660,7 +2660,7 @@
         <x:v>120096</x:v>
       </x:c>
       <x:c r="E100" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F100" s="38" t="str">
         <x:v>sf1</x:v>
@@ -2681,7 +2681,7 @@
         <x:v>120097</x:v>
       </x:c>
       <x:c r="E101" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F101" s="38" t="str">
         <x:v>sf2</x:v>
@@ -2702,7 +2702,7 @@
         <x:v>120098</x:v>
       </x:c>
       <x:c r="E102" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F102" s="38" t="str">
         <x:v>sf3</x:v>
@@ -2723,7 +2723,7 @@
         <x:v>120099</x:v>
       </x:c>
       <x:c r="E103" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F103" s="38" t="str">
         <x:v>sw</x:v>
@@ -2744,7 +2744,7 @@
         <x:v>120100</x:v>
       </x:c>
       <x:c r="E104" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F104" s="38" t="str">
         <x:v>zd</x:v>
@@ -2765,7 +2765,7 @@
         <x:v>120101</x:v>
       </x:c>
       <x:c r="E105" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F105" s="38" t="str">
         <x:v>bj</x:v>
@@ -2807,7 +2807,7 @@
         <x:v>120103</x:v>
       </x:c>
       <x:c r="E107" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F107" s="38" t="str">
         <x:v>gj</x:v>
@@ -2849,7 +2849,7 @@
         <x:v>120105</x:v>
       </x:c>
       <x:c r="E109" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F109" s="38" t="str">
         <x:v>sf1</x:v>
@@ -2870,7 +2870,7 @@
         <x:v>120106</x:v>
       </x:c>
       <x:c r="E110" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F110" s="38" t="str">
         <x:v>sf2</x:v>
@@ -2891,7 +2891,7 @@
         <x:v>120107</x:v>
       </x:c>
       <x:c r="E111" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F111" s="38" t="str">
         <x:v>sf3</x:v>
@@ -2912,7 +2912,7 @@
         <x:v>120108</x:v>
       </x:c>
       <x:c r="E112" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F112" s="38" t="str">
         <x:v>sw</x:v>
@@ -2933,7 +2933,7 @@
         <x:v>120109</x:v>
       </x:c>
       <x:c r="E113" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F113" s="38" t="str">
         <x:v>zd</x:v>
@@ -2954,7 +2954,7 @@
         <x:v>120110</x:v>
       </x:c>
       <x:c r="E114" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F114" s="38" t="str">
         <x:v>bj</x:v>
@@ -2996,7 +2996,7 @@
         <x:v>120112</x:v>
       </x:c>
       <x:c r="E116" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F116" s="38" t="str">
         <x:v>gj</x:v>
@@ -3038,7 +3038,7 @@
         <x:v>120114</x:v>
       </x:c>
       <x:c r="E118" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F118" s="38" t="str">
         <x:v>sf1</x:v>
@@ -3059,7 +3059,7 @@
         <x:v>120115</x:v>
       </x:c>
       <x:c r="E119" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F119" s="38" t="str">
         <x:v>sf2</x:v>
@@ -3080,7 +3080,7 @@
         <x:v>120116</x:v>
       </x:c>
       <x:c r="E120" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F120" s="38" t="str">
         <x:v>sf3</x:v>
@@ -3101,7 +3101,7 @@
         <x:v>120117</x:v>
       </x:c>
       <x:c r="E121" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F121" s="38" t="str">
         <x:v>sw</x:v>
@@ -3122,7 +3122,7 @@
         <x:v>120118</x:v>
       </x:c>
       <x:c r="E122" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F122" s="38" t="str">
         <x:v>zd</x:v>
@@ -3143,7 +3143,7 @@
         <x:v>120119</x:v>
       </x:c>
       <x:c r="E123" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F123" s="38" t="str">
         <x:v>bj</x:v>
@@ -3185,7 +3185,7 @@
         <x:v>120121</x:v>
       </x:c>
       <x:c r="E125" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F125" s="38" t="str">
         <x:v>gj</x:v>
@@ -3227,7 +3227,7 @@
         <x:v>120123</x:v>
       </x:c>
       <x:c r="E127" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F127" s="38" t="str">
         <x:v>sf1</x:v>
@@ -3248,7 +3248,7 @@
         <x:v>120124</x:v>
       </x:c>
       <x:c r="E128" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F128" s="38" t="str">
         <x:v>sf2</x:v>
@@ -3269,7 +3269,7 @@
         <x:v>120125</x:v>
       </x:c>
       <x:c r="E129" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F129" s="38" t="str">
         <x:v>sf3</x:v>
@@ -3290,7 +3290,7 @@
         <x:v>120126</x:v>
       </x:c>
       <x:c r="E130" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F130" s="38" t="str">
         <x:v>sw</x:v>
@@ -3311,7 +3311,7 @@
         <x:v>120127</x:v>
       </x:c>
       <x:c r="E131" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F131" s="38" t="str">
         <x:v>zd</x:v>
@@ -3332,7 +3332,7 @@
         <x:v>120128</x:v>
       </x:c>
       <x:c r="E132" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F132" s="38" t="str">
         <x:v>bj</x:v>
@@ -3374,7 +3374,7 @@
         <x:v>120130</x:v>
       </x:c>
       <x:c r="E134" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F134" s="38" t="str">
         <x:v>gj</x:v>
@@ -3416,7 +3416,7 @@
         <x:v>120132</x:v>
       </x:c>
       <x:c r="E136" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F136" s="38" t="str">
         <x:v>sf1</x:v>
@@ -3437,7 +3437,7 @@
         <x:v>120133</x:v>
       </x:c>
       <x:c r="E137" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F137" s="38" t="str">
         <x:v>sf2</x:v>
@@ -3458,7 +3458,7 @@
         <x:v>120134</x:v>
       </x:c>
       <x:c r="E138" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F138" s="38" t="str">
         <x:v>sf3</x:v>
@@ -3479,7 +3479,7 @@
         <x:v>120135</x:v>
       </x:c>
       <x:c r="E139" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F139" s="38" t="str">
         <x:v>sw</x:v>
@@ -3500,7 +3500,7 @@
         <x:v>120136</x:v>
       </x:c>
       <x:c r="E140" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F140" s="38" t="str">
         <x:v>zd</x:v>
@@ -3521,7 +3521,7 @@
         <x:v>120137</x:v>
       </x:c>
       <x:c r="E141" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F141" s="38" t="str">
         <x:v>bj</x:v>
@@ -3563,7 +3563,7 @@
         <x:v>120139</x:v>
       </x:c>
       <x:c r="E143" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F143" s="38" t="str">
         <x:v>gj</x:v>
@@ -3605,7 +3605,7 @@
         <x:v>120141</x:v>
       </x:c>
       <x:c r="E145" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F145" s="38" t="str">
         <x:v>sf1</x:v>
@@ -3626,7 +3626,7 @@
         <x:v>120142</x:v>
       </x:c>
       <x:c r="E146" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F146" s="38" t="str">
         <x:v>sf2</x:v>
@@ -3647,7 +3647,7 @@
         <x:v>120143</x:v>
       </x:c>
       <x:c r="E147" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F147" s="38" t="str">
         <x:v>sf3</x:v>
@@ -3668,7 +3668,7 @@
         <x:v>120144</x:v>
       </x:c>
       <x:c r="E148" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F148" s="38" t="str">
         <x:v>sf4</x:v>
@@ -3689,7 +3689,7 @@
         <x:v>120145</x:v>
       </x:c>
       <x:c r="E149" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F149" s="38" t="str">
         <x:v>sw</x:v>
@@ -3710,7 +3710,7 @@
         <x:v>120146</x:v>
       </x:c>
       <x:c r="E150" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F150" s="38" t="str">
         <x:v>zd</x:v>
@@ -3731,7 +3731,7 @@
         <x:v>120147</x:v>
       </x:c>
       <x:c r="E151" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F151" s="38" t="str">
         <x:v>bj</x:v>
@@ -3773,7 +3773,7 @@
         <x:v>120149</x:v>
       </x:c>
       <x:c r="E153" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F153" s="38" t="str">
         <x:v>gj</x:v>
@@ -3815,7 +3815,7 @@
         <x:v>120151</x:v>
       </x:c>
       <x:c r="E155" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F155" s="38" t="str">
         <x:v>sf1</x:v>
@@ -3836,7 +3836,7 @@
         <x:v>120152</x:v>
       </x:c>
       <x:c r="E156" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F156" s="38" t="str">
         <x:v>sf2</x:v>
@@ -3857,7 +3857,7 @@
         <x:v>120153</x:v>
       </x:c>
       <x:c r="E157" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F157" s="38" t="str">
         <x:v>sf3</x:v>
@@ -3878,7 +3878,7 @@
         <x:v>120154</x:v>
       </x:c>
       <x:c r="E158" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F158" s="38" t="str">
         <x:v>sf4</x:v>
@@ -3899,7 +3899,7 @@
         <x:v>120155</x:v>
       </x:c>
       <x:c r="E159" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F159" s="38" t="str">
         <x:v>sw</x:v>
@@ -3920,7 +3920,7 @@
         <x:v>120156</x:v>
       </x:c>
       <x:c r="E160" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F160" s="38" t="str">
         <x:v>zd</x:v>
@@ -3941,7 +3941,7 @@
         <x:v>120157</x:v>
       </x:c>
       <x:c r="E161" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F161" s="38" t="str">
         <x:v>bj</x:v>
@@ -3983,7 +3983,7 @@
         <x:v>120159</x:v>
       </x:c>
       <x:c r="E163" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F163" s="38" t="str">
         <x:v>gj</x:v>
@@ -4025,7 +4025,7 @@
         <x:v>120161</x:v>
       </x:c>
       <x:c r="E165" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F165" s="38" t="str">
         <x:v>sf1</x:v>
@@ -4046,7 +4046,7 @@
         <x:v>120162</x:v>
       </x:c>
       <x:c r="E166" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F166" s="38" t="str">
         <x:v>sf2</x:v>
@@ -4067,7 +4067,7 @@
         <x:v>120163</x:v>
       </x:c>
       <x:c r="E167" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F167" s="38" t="str">
         <x:v>sf3</x:v>
@@ -4088,7 +4088,7 @@
         <x:v>120164</x:v>
       </x:c>
       <x:c r="E168" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F168" s="38" t="str">
         <x:v>sw</x:v>
@@ -4109,7 +4109,7 @@
         <x:v>120165</x:v>
       </x:c>
       <x:c r="E169" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F169" s="38" t="str">
         <x:v>zd</x:v>
@@ -4130,7 +4130,7 @@
         <x:v>120166</x:v>
       </x:c>
       <x:c r="E170" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F170" s="38" t="str">
         <x:v>bj</x:v>
@@ -4172,7 +4172,7 @@
         <x:v>120168</x:v>
       </x:c>
       <x:c r="E172" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F172" s="38" t="str">
         <x:v>gj</x:v>
@@ -4214,7 +4214,7 @@
         <x:v>120170</x:v>
       </x:c>
       <x:c r="E174" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F174" s="38" t="str">
         <x:v>sf1</x:v>
@@ -4235,7 +4235,7 @@
         <x:v>120171</x:v>
       </x:c>
       <x:c r="E175" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F175" s="38" t="str">
         <x:v>sf2</x:v>
@@ -4256,7 +4256,7 @@
         <x:v>120172</x:v>
       </x:c>
       <x:c r="E176" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F176" s="38" t="str">
         <x:v>sf3</x:v>
@@ -4277,7 +4277,7 @@
         <x:v>120173</x:v>
       </x:c>
       <x:c r="E177" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F177" s="38" t="str">
         <x:v>sw</x:v>
@@ -4298,7 +4298,7 @@
         <x:v>120174</x:v>
       </x:c>
       <x:c r="E178" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F178" s="38" t="str">
         <x:v>zd</x:v>
@@ -4319,7 +4319,7 @@
         <x:v>120175</x:v>
       </x:c>
       <x:c r="E179" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F179" s="38" t="str">
         <x:v>bj</x:v>
@@ -4361,7 +4361,7 @@
         <x:v>120177</x:v>
       </x:c>
       <x:c r="E181" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F181" s="38" t="str">
         <x:v>gj</x:v>
@@ -4403,7 +4403,7 @@
         <x:v>120179</x:v>
       </x:c>
       <x:c r="E183" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F183" s="38" t="str">
         <x:v>sf1</x:v>
@@ -4424,7 +4424,7 @@
         <x:v>120180</x:v>
       </x:c>
       <x:c r="E184" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F184" s="38" t="str">
         <x:v>sf2</x:v>
@@ -4445,7 +4445,7 @@
         <x:v>120181</x:v>
       </x:c>
       <x:c r="E185" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F185" s="38" t="str">
         <x:v>sf3</x:v>
@@ -4466,7 +4466,7 @@
         <x:v>120182</x:v>
       </x:c>
       <x:c r="E186" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F186" s="38" t="str">
         <x:v>sw</x:v>
@@ -4487,7 +4487,7 @@
         <x:v>120183</x:v>
       </x:c>
       <x:c r="E187" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F187" s="38" t="str">
         <x:v>zd</x:v>
@@ -4508,7 +4508,7 @@
         <x:v>120184</x:v>
       </x:c>
       <x:c r="E188" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F188" s="38" t="str">
         <x:v>bj</x:v>
@@ -4550,7 +4550,7 @@
         <x:v>120186</x:v>
       </x:c>
       <x:c r="E190" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F190" s="38" t="str">
         <x:v>gj</x:v>
@@ -4592,7 +4592,7 @@
         <x:v>120188</x:v>
       </x:c>
       <x:c r="E192" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F192" s="38" t="str">
         <x:v>sf1</x:v>
@@ -4613,7 +4613,7 @@
         <x:v>120189</x:v>
       </x:c>
       <x:c r="E193" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F193" s="38" t="str">
         <x:v>sf2</x:v>
@@ -4634,7 +4634,7 @@
         <x:v>120190</x:v>
       </x:c>
       <x:c r="E194" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F194" s="38" t="str">
         <x:v>sf3</x:v>
@@ -4655,7 +4655,7 @@
         <x:v>120191</x:v>
       </x:c>
       <x:c r="E195" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F195" s="38" t="str">
         <x:v>sw</x:v>
@@ -4676,7 +4676,7 @@
         <x:v>120192</x:v>
       </x:c>
       <x:c r="E196" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F196" s="38" t="str">
         <x:v>zd</x:v>
@@ -4697,7 +4697,7 @@
         <x:v>120193</x:v>
       </x:c>
       <x:c r="E197" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F197" s="38" t="str">
         <x:v>bj</x:v>
@@ -4739,7 +4739,7 @@
         <x:v>120195</x:v>
       </x:c>
       <x:c r="E199" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F199" s="38" t="str">
         <x:v>gj</x:v>
@@ -4781,7 +4781,7 @@
         <x:v>120197</x:v>
       </x:c>
       <x:c r="E201" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F201" s="38" t="str">
         <x:v>sf1</x:v>
@@ -4802,7 +4802,7 @@
         <x:v>120198</x:v>
       </x:c>
       <x:c r="E202" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F202" s="38" t="str">
         <x:v>sf2</x:v>
@@ -4823,7 +4823,7 @@
         <x:v>120199</x:v>
       </x:c>
       <x:c r="E203" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F203" s="38" t="str">
         <x:v>sf3</x:v>
@@ -4844,7 +4844,7 @@
         <x:v>120200</x:v>
       </x:c>
       <x:c r="E204" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F204" s="38" t="str">
         <x:v>sw</x:v>
@@ -4865,7 +4865,7 @@
         <x:v>120201</x:v>
       </x:c>
       <x:c r="E205" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F205" s="38" t="str">
         <x:v>zd</x:v>
@@ -4886,7 +4886,7 @@
         <x:v>120202</x:v>
       </x:c>
       <x:c r="E206" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F206" s="38" t="str">
         <x:v>bj</x:v>
@@ -4928,7 +4928,7 @@
         <x:v>120204</x:v>
       </x:c>
       <x:c r="E208" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F208" s="38" t="str">
         <x:v>gj</x:v>
@@ -4970,7 +4970,7 @@
         <x:v>120206</x:v>
       </x:c>
       <x:c r="E210" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F210" s="38" t="str">
         <x:v>sf1</x:v>
@@ -4991,7 +4991,7 @@
         <x:v>120207</x:v>
       </x:c>
       <x:c r="E211" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F211" s="38" t="str">
         <x:v>sf2</x:v>
@@ -5012,7 +5012,7 @@
         <x:v>120208</x:v>
       </x:c>
       <x:c r="E212" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F212" s="38" t="str">
         <x:v>sf3</x:v>
@@ -5033,7 +5033,7 @@
         <x:v>120209</x:v>
       </x:c>
       <x:c r="E213" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F213" s="38" t="str">
         <x:v>sw</x:v>
@@ -5054,7 +5054,7 @@
         <x:v>120210</x:v>
       </x:c>
       <x:c r="E214" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F214" s="38" t="str">
         <x:v>zd</x:v>
@@ -5075,7 +5075,7 @@
         <x:v>120211</x:v>
       </x:c>
       <x:c r="E215" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F215" s="38" t="str">
         <x:v>bj</x:v>
@@ -5117,7 +5117,7 @@
         <x:v>120213</x:v>
       </x:c>
       <x:c r="E217" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F217" s="38" t="str">
         <x:v>gj</x:v>
@@ -5159,7 +5159,7 @@
         <x:v>120215</x:v>
       </x:c>
       <x:c r="E219" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F219" s="38" t="str">
         <x:v>sf1</x:v>
@@ -5180,7 +5180,7 @@
         <x:v>120216</x:v>
       </x:c>
       <x:c r="E220" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F220" s="38" t="str">
         <x:v>sf2</x:v>
@@ -5201,7 +5201,7 @@
         <x:v>120217</x:v>
       </x:c>
       <x:c r="E221" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F221" s="38" t="str">
         <x:v>sf3</x:v>
@@ -5222,7 +5222,7 @@
         <x:v>120218</x:v>
       </x:c>
       <x:c r="E222" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F222" s="38" t="str">
         <x:v>sw</x:v>
@@ -5243,7 +5243,7 @@
         <x:v>120219</x:v>
       </x:c>
       <x:c r="E223" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F223" s="38" t="str">
         <x:v>zd</x:v>
@@ -5264,7 +5264,7 @@
         <x:v>120220</x:v>
       </x:c>
       <x:c r="E224" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F224" s="38" t="str">
         <x:v>bj</x:v>
@@ -5306,7 +5306,7 @@
         <x:v>120222</x:v>
       </x:c>
       <x:c r="E226" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F226" s="38" t="str">
         <x:v>gj</x:v>
@@ -5348,7 +5348,7 @@
         <x:v>120224</x:v>
       </x:c>
       <x:c r="E228" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F228" s="38" t="str">
         <x:v>sf1</x:v>
@@ -5369,7 +5369,7 @@
         <x:v>120225</x:v>
       </x:c>
       <x:c r="E229" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F229" s="38" t="str">
         <x:v>sf2</x:v>
@@ -5390,7 +5390,7 @@
         <x:v>120226</x:v>
       </x:c>
       <x:c r="E230" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F230" s="38" t="str">
         <x:v>sf3</x:v>
@@ -5411,7 +5411,7 @@
         <x:v>120227</x:v>
       </x:c>
       <x:c r="E231" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F231" s="38" t="str">
         <x:v>sw</x:v>
@@ -5432,7 +5432,7 @@
         <x:v>120228</x:v>
       </x:c>
       <x:c r="E232" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F232" s="38" t="str">
         <x:v>zd</x:v>
@@ -5453,7 +5453,7 @@
         <x:v>120229</x:v>
       </x:c>
       <x:c r="E233" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F233" s="38" t="str">
         <x:v>bj</x:v>
@@ -5495,7 +5495,7 @@
         <x:v>120231</x:v>
       </x:c>
       <x:c r="E235" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F235" s="38" t="str">
         <x:v>gj</x:v>
@@ -5537,7 +5537,7 @@
         <x:v>120233</x:v>
       </x:c>
       <x:c r="E237" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F237" s="38" t="str">
         <x:v>sf1</x:v>
@@ -5558,7 +5558,7 @@
         <x:v>120234</x:v>
       </x:c>
       <x:c r="E238" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F238" s="38" t="str">
         <x:v>sf2</x:v>
@@ -5579,7 +5579,7 @@
         <x:v>120235</x:v>
       </x:c>
       <x:c r="E239" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F239" s="38" t="str">
         <x:v>sf3</x:v>
@@ -5600,7 +5600,7 @@
         <x:v>120236</x:v>
       </x:c>
       <x:c r="E240" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F240" s="38" t="str">
         <x:v>sw</x:v>
@@ -5621,7 +5621,7 @@
         <x:v>120237</x:v>
       </x:c>
       <x:c r="E241" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F241" s="38" t="str">
         <x:v>zd</x:v>
@@ -5642,7 +5642,7 @@
         <x:v>120238</x:v>
       </x:c>
       <x:c r="E242" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F242" s="38" t="str">
         <x:v>bj</x:v>
@@ -5684,7 +5684,7 @@
         <x:v>120240</x:v>
       </x:c>
       <x:c r="E244" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F244" s="38" t="str">
         <x:v>gj</x:v>
@@ -5726,7 +5726,7 @@
         <x:v>120242</x:v>
       </x:c>
       <x:c r="E246" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F246" s="38" t="str">
         <x:v>sf1</x:v>
@@ -5747,7 +5747,7 @@
         <x:v>120243</x:v>
       </x:c>
       <x:c r="E247" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F247" s="38" t="str">
         <x:v>sf2</x:v>
@@ -5768,7 +5768,7 @@
         <x:v>120244</x:v>
       </x:c>
       <x:c r="E248" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F248" s="38" t="str">
         <x:v>sf3</x:v>
@@ -5789,7 +5789,7 @@
         <x:v>120245</x:v>
       </x:c>
       <x:c r="E249" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F249" s="38" t="str">
         <x:v>sw</x:v>
@@ -5810,7 +5810,7 @@
         <x:v>120246</x:v>
       </x:c>
       <x:c r="E250" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F250" s="38" t="str">
         <x:v>zd</x:v>
@@ -5831,7 +5831,7 @@
         <x:v>120247</x:v>
       </x:c>
       <x:c r="E251" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F251" s="38" t="str">
         <x:v>bj</x:v>
@@ -5873,7 +5873,7 @@
         <x:v>120249</x:v>
       </x:c>
       <x:c r="E253" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F253" s="38" t="str">
         <x:v>gj</x:v>
@@ -5915,7 +5915,7 @@
         <x:v>120251</x:v>
       </x:c>
       <x:c r="E255" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F255" s="38" t="str">
         <x:v>sf1</x:v>
@@ -5936,7 +5936,7 @@
         <x:v>120252</x:v>
       </x:c>
       <x:c r="E256" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F256" s="38" t="str">
         <x:v>sf2</x:v>
@@ -5957,7 +5957,7 @@
         <x:v>120253</x:v>
       </x:c>
       <x:c r="E257" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F257" s="38" t="str">
         <x:v>sf3</x:v>
@@ -5978,7 +5978,7 @@
         <x:v>120254</x:v>
       </x:c>
       <x:c r="E258" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F258" s="38" t="str">
         <x:v>sw</x:v>
@@ -5999,7 +5999,7 @@
         <x:v>120255</x:v>
       </x:c>
       <x:c r="E259" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F259" s="38" t="str">
         <x:v>zd</x:v>
@@ -6020,7 +6020,7 @@
         <x:v>120256</x:v>
       </x:c>
       <x:c r="E260" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F260" s="38" t="str">
         <x:v>bj</x:v>
@@ -6062,7 +6062,7 @@
         <x:v>120258</x:v>
       </x:c>
       <x:c r="E262" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F262" s="38" t="str">
         <x:v>gj</x:v>
@@ -6104,7 +6104,7 @@
         <x:v>120260</x:v>
       </x:c>
       <x:c r="E264" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F264" s="38" t="str">
         <x:v>sf1</x:v>
@@ -6125,7 +6125,7 @@
         <x:v>120261</x:v>
       </x:c>
       <x:c r="E265" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F265" s="38" t="str">
         <x:v>sf2</x:v>
@@ -6146,7 +6146,7 @@
         <x:v>120262</x:v>
       </x:c>
       <x:c r="E266" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F266" s="38" t="str">
         <x:v>sf3</x:v>
@@ -6167,7 +6167,7 @@
         <x:v>120263</x:v>
       </x:c>
       <x:c r="E267" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F267" s="38" t="str">
         <x:v>sw</x:v>
@@ -6188,7 +6188,7 @@
         <x:v>120264</x:v>
       </x:c>
       <x:c r="E268" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F268" s="38" t="str">
         <x:v>zd</x:v>
@@ -6209,7 +6209,7 @@
         <x:v>120265</x:v>
       </x:c>
       <x:c r="E269" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F269" s="38" t="str">
         <x:v>bj</x:v>
@@ -6251,7 +6251,7 @@
         <x:v>120267</x:v>
       </x:c>
       <x:c r="E271" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F271" s="38" t="str">
         <x:v>gj</x:v>
@@ -6293,7 +6293,7 @@
         <x:v>120269</x:v>
       </x:c>
       <x:c r="E273" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F273" s="38" t="str">
         <x:v>sf1</x:v>
@@ -6314,7 +6314,7 @@
         <x:v>120270</x:v>
       </x:c>
       <x:c r="E274" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F274" s="38" t="str">
         <x:v>sf2</x:v>
@@ -6335,7 +6335,7 @@
         <x:v>120271</x:v>
       </x:c>
       <x:c r="E275" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F275" s="38" t="str">
         <x:v>sf3</x:v>
@@ -6356,7 +6356,7 @@
         <x:v>120272</x:v>
       </x:c>
       <x:c r="E276" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F276" s="38" t="str">
         <x:v>sw</x:v>
@@ -6377,7 +6377,7 @@
         <x:v>120273</x:v>
       </x:c>
       <x:c r="E277" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F277" s="38" t="str">
         <x:v>zd</x:v>
@@ -7301,7 +7301,7 @@
         <x:v>220001</x:v>
       </x:c>
       <x:c r="E321" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F321" s="38" t="str">
         <x:v>bj</x:v>
@@ -7322,7 +7322,7 @@
         <x:v>220002</x:v>
       </x:c>
       <x:c r="E322" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Attack</x:v>
       </x:c>
       <x:c r="F322" s="38" t="str">
         <x:v>gj</x:v>
@@ -7364,7 +7364,7 @@
         <x:v>220004</x:v>
       </x:c>
       <x:c r="E324" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F324" s="38" t="str">
         <x:v>sf1</x:v>
@@ -7385,7 +7385,7 @@
         <x:v>220005</x:v>
       </x:c>
       <x:c r="E325" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F325" s="38" t="str">
         <x:v>sf2</x:v>
@@ -7406,7 +7406,7 @@
         <x:v>220006</x:v>
       </x:c>
       <x:c r="E326" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F326" s="38" t="str">
         <x:v>sw</x:v>
@@ -7427,13 +7427,13 @@
         <x:v>220007</x:v>
       </x:c>
       <x:c r="E327" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F327" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G327" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="328">
@@ -7448,13 +7448,13 @@
         <x:v>220008</x:v>
       </x:c>
       <x:c r="E328" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F328" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G328" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="329">
@@ -7469,7 +7469,7 @@
         <x:v>220009</x:v>
       </x:c>
       <x:c r="E329" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F329" s="38" t="str">
         <x:v>bj</x:v>
@@ -7490,7 +7490,7 @@
         <x:v>220010</x:v>
       </x:c>
       <x:c r="E330" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F330" s="38" t="str">
         <x:v>gj</x:v>
@@ -7532,7 +7532,7 @@
         <x:v>220012</x:v>
       </x:c>
       <x:c r="E332" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F332" s="38" t="str">
         <x:v>sf1</x:v>
@@ -7553,7 +7553,7 @@
         <x:v>220013</x:v>
       </x:c>
       <x:c r="E333" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F333" s="38" t="str">
         <x:v>sf2</x:v>
@@ -7574,7 +7574,7 @@
         <x:v>220014</x:v>
       </x:c>
       <x:c r="E334" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F334" s="38" t="str">
         <x:v>sw</x:v>
@@ -7595,13 +7595,13 @@
         <x:v>220015</x:v>
       </x:c>
       <x:c r="E335" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F335" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G335" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="336">
@@ -7616,13 +7616,13 @@
         <x:v>220016</x:v>
       </x:c>
       <x:c r="E336" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F336" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G336" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="337">
@@ -7637,7 +7637,7 @@
         <x:v>220017</x:v>
       </x:c>
       <x:c r="E337" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F337" s="38" t="str">
         <x:v>bj</x:v>
@@ -7658,7 +7658,7 @@
         <x:v>220018</x:v>
       </x:c>
       <x:c r="E338" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F338" s="38" t="str">
         <x:v>gj</x:v>
@@ -7700,7 +7700,7 @@
         <x:v>220020</x:v>
       </x:c>
       <x:c r="E340" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F340" s="38" t="str">
         <x:v>sf1</x:v>
@@ -7721,7 +7721,7 @@
         <x:v>220021</x:v>
       </x:c>
       <x:c r="E341" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F341" s="38" t="str">
         <x:v>sf2</x:v>
@@ -7742,7 +7742,7 @@
         <x:v>220022</x:v>
       </x:c>
       <x:c r="E342" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F342" s="38" t="str">
         <x:v>sw</x:v>
@@ -7763,13 +7763,13 @@
         <x:v>220023</x:v>
       </x:c>
       <x:c r="E343" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F343" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G343" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="344">
@@ -7784,7 +7784,7 @@
         <x:v>220024</x:v>
       </x:c>
       <x:c r="E344" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F344" s="38" t="str">
         <x:v>bj</x:v>
@@ -7805,7 +7805,7 @@
         <x:v>220025</x:v>
       </x:c>
       <x:c r="E345" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F345" s="38" t="str">
         <x:v>gj</x:v>
@@ -7847,7 +7847,7 @@
         <x:v>220027</x:v>
       </x:c>
       <x:c r="E347" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F347" s="38" t="str">
         <x:v>sf1</x:v>
@@ -7868,7 +7868,7 @@
         <x:v>220028</x:v>
       </x:c>
       <x:c r="E348" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F348" s="38" t="str">
         <x:v>sf2</x:v>
@@ -7889,7 +7889,7 @@
         <x:v>220029</x:v>
       </x:c>
       <x:c r="E349" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F349" s="38" t="str">
         <x:v>sw</x:v>
@@ -7910,13 +7910,13 @@
         <x:v>220030</x:v>
       </x:c>
       <x:c r="E350" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F350" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G350" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="351">
@@ -7931,7 +7931,7 @@
         <x:v>220031</x:v>
       </x:c>
       <x:c r="E351" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F351" s="38" t="str">
         <x:v>bj</x:v>
@@ -7952,7 +7952,7 @@
         <x:v>220032</x:v>
       </x:c>
       <x:c r="E352" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F352" s="38" t="str">
         <x:v>gj</x:v>
@@ -7994,7 +7994,7 @@
         <x:v>220034</x:v>
       </x:c>
       <x:c r="E354" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F354" s="38" t="str">
         <x:v>sf1</x:v>
@@ -8015,7 +8015,7 @@
         <x:v>220035</x:v>
       </x:c>
       <x:c r="E355" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F355" s="38" t="str">
         <x:v>sf2</x:v>
@@ -8036,7 +8036,7 @@
         <x:v>220036</x:v>
       </x:c>
       <x:c r="E356" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F356" s="38" t="str">
         <x:v>sw</x:v>
@@ -8057,13 +8057,13 @@
         <x:v>220037</x:v>
       </x:c>
       <x:c r="E357" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F357" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G357" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="358">
@@ -8078,7 +8078,7 @@
         <x:v>220038</x:v>
       </x:c>
       <x:c r="E358" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F358" s="38" t="str">
         <x:v>bj</x:v>
@@ -8099,7 +8099,7 @@
         <x:v>220039</x:v>
       </x:c>
       <x:c r="E359" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F359" s="38" t="str">
         <x:v>gj</x:v>
@@ -8141,7 +8141,7 @@
         <x:v>220041</x:v>
       </x:c>
       <x:c r="E361" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F361" s="38" t="str">
         <x:v>sf1</x:v>
@@ -8162,7 +8162,7 @@
         <x:v>220042</x:v>
       </x:c>
       <x:c r="E362" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F362" s="38" t="str">
         <x:v>sf2</x:v>
@@ -8183,7 +8183,7 @@
         <x:v>220043</x:v>
       </x:c>
       <x:c r="E363" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F363" s="38" t="str">
         <x:v>sw</x:v>
@@ -8204,13 +8204,13 @@
         <x:v>220044</x:v>
       </x:c>
       <x:c r="E364" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F364" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G364" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="365">
@@ -8225,7 +8225,7 @@
         <x:v>220045</x:v>
       </x:c>
       <x:c r="E365" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F365" s="38" t="str">
         <x:v>bj</x:v>
@@ -8246,7 +8246,7 @@
         <x:v>220046</x:v>
       </x:c>
       <x:c r="E366" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F366" s="38" t="str">
         <x:v>gj</x:v>
@@ -8288,7 +8288,7 @@
         <x:v>220048</x:v>
       </x:c>
       <x:c r="E368" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F368" s="38" t="str">
         <x:v>sf1</x:v>
@@ -8309,7 +8309,7 @@
         <x:v>220049</x:v>
       </x:c>
       <x:c r="E369" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F369" s="38" t="str">
         <x:v>sf2</x:v>
@@ -8330,7 +8330,7 @@
         <x:v>220050</x:v>
       </x:c>
       <x:c r="E370" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F370" s="38" t="str">
         <x:v>sw</x:v>
@@ -8351,13 +8351,13 @@
         <x:v>220051</x:v>
       </x:c>
       <x:c r="E371" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F371" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G371" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="372">
@@ -8372,7 +8372,7 @@
         <x:v>220052</x:v>
       </x:c>
       <x:c r="E372" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F372" s="38" t="str">
         <x:v>bj</x:v>
@@ -8393,7 +8393,7 @@
         <x:v>220053</x:v>
       </x:c>
       <x:c r="E373" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F373" s="38" t="str">
         <x:v>gj</x:v>
@@ -8435,7 +8435,7 @@
         <x:v>220055</x:v>
       </x:c>
       <x:c r="E375" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F375" s="38" t="str">
         <x:v>sf1</x:v>
@@ -8456,7 +8456,7 @@
         <x:v>220056</x:v>
       </x:c>
       <x:c r="E376" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F376" s="38" t="str">
         <x:v>sf2</x:v>
@@ -8477,7 +8477,7 @@
         <x:v>220057</x:v>
       </x:c>
       <x:c r="E377" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F377" s="38" t="str">
         <x:v>sw</x:v>
@@ -8498,13 +8498,13 @@
         <x:v>220058</x:v>
       </x:c>
       <x:c r="E378" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F378" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G378" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="379">
@@ -8519,7 +8519,7 @@
         <x:v>220059</x:v>
       </x:c>
       <x:c r="E379" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F379" s="38" t="str">
         <x:v>bj</x:v>
@@ -8540,7 +8540,7 @@
         <x:v>220060</x:v>
       </x:c>
       <x:c r="E380" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F380" s="38" t="str">
         <x:v>gj</x:v>
@@ -8582,7 +8582,7 @@
         <x:v>220062</x:v>
       </x:c>
       <x:c r="E382" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F382" s="38" t="str">
         <x:v>sf1</x:v>
@@ -8603,7 +8603,7 @@
         <x:v>220063</x:v>
       </x:c>
       <x:c r="E383" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F383" s="38" t="str">
         <x:v>sf2</x:v>
@@ -8624,7 +8624,7 @@
         <x:v>220064</x:v>
       </x:c>
       <x:c r="E384" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F384" s="38" t="str">
         <x:v>sw</x:v>
@@ -8645,13 +8645,13 @@
         <x:v>220065</x:v>
       </x:c>
       <x:c r="E385" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F385" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G385" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="386">
@@ -8666,7 +8666,7 @@
         <x:v>220066</x:v>
       </x:c>
       <x:c r="E386" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F386" s="38" t="str">
         <x:v>bj</x:v>
@@ -8687,7 +8687,7 @@
         <x:v>220067</x:v>
       </x:c>
       <x:c r="E387" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F387" s="38" t="str">
         <x:v>gj</x:v>
@@ -8729,7 +8729,7 @@
         <x:v>220069</x:v>
       </x:c>
       <x:c r="E389" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F389" s="38" t="str">
         <x:v>sf1</x:v>
@@ -8750,7 +8750,7 @@
         <x:v>220070</x:v>
       </x:c>
       <x:c r="E390" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F390" s="38" t="str">
         <x:v>sf2</x:v>
@@ -8771,7 +8771,7 @@
         <x:v>220071</x:v>
       </x:c>
       <x:c r="E391" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F391" s="38" t="str">
         <x:v>sw</x:v>
@@ -8792,13 +8792,13 @@
         <x:v>220072</x:v>
       </x:c>
       <x:c r="E392" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F392" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G392" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="393">
@@ -8813,7 +8813,7 @@
         <x:v>220073</x:v>
       </x:c>
       <x:c r="E393" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F393" s="38" t="str">
         <x:v>bj</x:v>
@@ -8834,7 +8834,7 @@
         <x:v>220074</x:v>
       </x:c>
       <x:c r="E394" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F394" s="38" t="str">
         <x:v>gj</x:v>
@@ -8876,7 +8876,7 @@
         <x:v>220076</x:v>
       </x:c>
       <x:c r="E396" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F396" s="38" t="str">
         <x:v>sf1</x:v>
@@ -8897,7 +8897,7 @@
         <x:v>220077</x:v>
       </x:c>
       <x:c r="E397" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F397" s="38" t="str">
         <x:v>sf2</x:v>
@@ -8918,7 +8918,7 @@
         <x:v>220078</x:v>
       </x:c>
       <x:c r="E398" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F398" s="38" t="str">
         <x:v>sw</x:v>
@@ -8939,13 +8939,13 @@
         <x:v>220079</x:v>
       </x:c>
       <x:c r="E399" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F399" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G399" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="400">
@@ -8960,7 +8960,7 @@
         <x:v>220080</x:v>
       </x:c>
       <x:c r="E400" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F400" s="38" t="str">
         <x:v>bj</x:v>
@@ -8981,7 +8981,7 @@
         <x:v>220081</x:v>
       </x:c>
       <x:c r="E401" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F401" s="38" t="str">
         <x:v>gj</x:v>
@@ -9023,7 +9023,7 @@
         <x:v>220083</x:v>
       </x:c>
       <x:c r="E403" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F403" s="38" t="str">
         <x:v>sf1</x:v>
@@ -9044,7 +9044,7 @@
         <x:v>220084</x:v>
       </x:c>
       <x:c r="E404" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F404" s="38" t="str">
         <x:v>sf2</x:v>
@@ -9065,7 +9065,7 @@
         <x:v>220085</x:v>
       </x:c>
       <x:c r="E405" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F405" s="38" t="str">
         <x:v>sw</x:v>
@@ -9086,13 +9086,13 @@
         <x:v>220086</x:v>
       </x:c>
       <x:c r="E406" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F406" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G406" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="407">
@@ -9107,7 +9107,7 @@
         <x:v>220087</x:v>
       </x:c>
       <x:c r="E407" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F407" s="38" t="str">
         <x:v>bj</x:v>
@@ -9128,7 +9128,7 @@
         <x:v>220088</x:v>
       </x:c>
       <x:c r="E408" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F408" s="38" t="str">
         <x:v>gj</x:v>
@@ -9170,7 +9170,7 @@
         <x:v>220090</x:v>
       </x:c>
       <x:c r="E410" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F410" s="38" t="str">
         <x:v>sf1</x:v>
@@ -9191,7 +9191,7 @@
         <x:v>220091</x:v>
       </x:c>
       <x:c r="E411" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F411" s="38" t="str">
         <x:v>sf2</x:v>
@@ -9212,7 +9212,7 @@
         <x:v>220092</x:v>
       </x:c>
       <x:c r="E412" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F412" s="38" t="str">
         <x:v>sw</x:v>
@@ -9233,13 +9233,13 @@
         <x:v>220093</x:v>
       </x:c>
       <x:c r="E413" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F413" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G413" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="414">
@@ -9254,7 +9254,7 @@
         <x:v>220094</x:v>
       </x:c>
       <x:c r="E414" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F414" s="38" t="str">
         <x:v>bj</x:v>
@@ -9275,7 +9275,7 @@
         <x:v>220095</x:v>
       </x:c>
       <x:c r="E415" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F415" s="38" t="str">
         <x:v>gj</x:v>
@@ -9317,7 +9317,7 @@
         <x:v>220097</x:v>
       </x:c>
       <x:c r="E417" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F417" s="38" t="str">
         <x:v>sf1</x:v>
@@ -9338,7 +9338,7 @@
         <x:v>220098</x:v>
       </x:c>
       <x:c r="E418" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F418" s="38" t="str">
         <x:v>sf2</x:v>
@@ -9359,7 +9359,7 @@
         <x:v>220099</x:v>
       </x:c>
       <x:c r="E419" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F419" s="38" t="str">
         <x:v>sw</x:v>
@@ -9380,13 +9380,13 @@
         <x:v>220100</x:v>
       </x:c>
       <x:c r="E420" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F420" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G420" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="421">
@@ -9401,7 +9401,7 @@
         <x:v>220101</x:v>
       </x:c>
       <x:c r="E421" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F421" s="38" t="str">
         <x:v>bj</x:v>
@@ -9422,7 +9422,7 @@
         <x:v>220102</x:v>
       </x:c>
       <x:c r="E422" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F422" s="38" t="str">
         <x:v>gj</x:v>
@@ -9464,7 +9464,7 @@
         <x:v>220104</x:v>
       </x:c>
       <x:c r="E424" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F424" s="38" t="str">
         <x:v>sf1</x:v>
@@ -9485,7 +9485,7 @@
         <x:v>220105</x:v>
       </x:c>
       <x:c r="E425" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F425" s="38" t="str">
         <x:v>sf2</x:v>
@@ -9506,7 +9506,7 @@
         <x:v>220106</x:v>
       </x:c>
       <x:c r="E426" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F426" s="38" t="str">
         <x:v>sw</x:v>
@@ -9527,13 +9527,13 @@
         <x:v>220107</x:v>
       </x:c>
       <x:c r="E427" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F427" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G427" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="428">
@@ -9548,7 +9548,7 @@
         <x:v>220108</x:v>
       </x:c>
       <x:c r="E428" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F428" s="38" t="str">
         <x:v>bj</x:v>
@@ -9569,7 +9569,7 @@
         <x:v>220109</x:v>
       </x:c>
       <x:c r="E429" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F429" s="38" t="str">
         <x:v>gj</x:v>
@@ -9611,7 +9611,7 @@
         <x:v>220111</x:v>
       </x:c>
       <x:c r="E431" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F431" s="38" t="str">
         <x:v>sf1</x:v>
@@ -9632,7 +9632,7 @@
         <x:v>220112</x:v>
       </x:c>
       <x:c r="E432" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F432" s="38" t="str">
         <x:v>sf2</x:v>
@@ -9653,7 +9653,7 @@
         <x:v>220113</x:v>
       </x:c>
       <x:c r="E433" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F433" s="38" t="str">
         <x:v>sw</x:v>
@@ -9674,13 +9674,13 @@
         <x:v>220114</x:v>
       </x:c>
       <x:c r="E434" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F434" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G434" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="435">
@@ -9695,7 +9695,7 @@
         <x:v>220115</x:v>
       </x:c>
       <x:c r="E435" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F435" s="38" t="str">
         <x:v>bj</x:v>
@@ -9716,7 +9716,7 @@
         <x:v>220116</x:v>
       </x:c>
       <x:c r="E436" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F436" s="38" t="str">
         <x:v>gj</x:v>
@@ -9758,7 +9758,7 @@
         <x:v>220118</x:v>
       </x:c>
       <x:c r="E438" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F438" s="38" t="str">
         <x:v>sf1</x:v>
@@ -9779,7 +9779,7 @@
         <x:v>220119</x:v>
       </x:c>
       <x:c r="E439" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F439" s="38" t="str">
         <x:v>sf2</x:v>
@@ -9800,7 +9800,7 @@
         <x:v>220120</x:v>
       </x:c>
       <x:c r="E440" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F440" s="38" t="str">
         <x:v>sw</x:v>
@@ -9821,13 +9821,13 @@
         <x:v>220121</x:v>
       </x:c>
       <x:c r="E441" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F441" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G441" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="442">
@@ -9842,7 +9842,7 @@
         <x:v>220122</x:v>
       </x:c>
       <x:c r="E442" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F442" s="38" t="str">
         <x:v>bj</x:v>
@@ -9863,7 +9863,7 @@
         <x:v>220123</x:v>
       </x:c>
       <x:c r="E443" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F443" s="38" t="str">
         <x:v>gj</x:v>
@@ -9905,7 +9905,7 @@
         <x:v>220125</x:v>
       </x:c>
       <x:c r="E445" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F445" s="38" t="str">
         <x:v>sf1</x:v>
@@ -9926,7 +9926,7 @@
         <x:v>220126</x:v>
       </x:c>
       <x:c r="E446" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F446" s="38" t="str">
         <x:v>sf2</x:v>
@@ -9947,7 +9947,7 @@
         <x:v>220127</x:v>
       </x:c>
       <x:c r="E447" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F447" s="38" t="str">
         <x:v>sw</x:v>
@@ -9968,13 +9968,13 @@
         <x:v>220128</x:v>
       </x:c>
       <x:c r="E448" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F448" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G448" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="449">
@@ -9989,7 +9989,7 @@
         <x:v>220129</x:v>
       </x:c>
       <x:c r="E449" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F449" s="38" t="str">
         <x:v>bj</x:v>
@@ -10010,7 +10010,7 @@
         <x:v>220130</x:v>
       </x:c>
       <x:c r="E450" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F450" s="38" t="str">
         <x:v>gj</x:v>
@@ -10052,7 +10052,7 @@
         <x:v>220132</x:v>
       </x:c>
       <x:c r="E452" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F452" s="38" t="str">
         <x:v>sf1</x:v>
@@ -10073,7 +10073,7 @@
         <x:v>220133</x:v>
       </x:c>
       <x:c r="E453" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F453" s="38" t="str">
         <x:v>sf2</x:v>
@@ -10094,7 +10094,7 @@
         <x:v>220134</x:v>
       </x:c>
       <x:c r="E454" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F454" s="38" t="str">
         <x:v>sw</x:v>
@@ -10115,13 +10115,13 @@
         <x:v>220135</x:v>
       </x:c>
       <x:c r="E455" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F455" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G455" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="456">
@@ -10136,7 +10136,7 @@
         <x:v>220136</x:v>
       </x:c>
       <x:c r="E456" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F456" s="38" t="str">
         <x:v>bj</x:v>
@@ -10157,7 +10157,7 @@
         <x:v>220137</x:v>
       </x:c>
       <x:c r="E457" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F457" s="38" t="str">
         <x:v>gj</x:v>
@@ -10199,7 +10199,7 @@
         <x:v>220139</x:v>
       </x:c>
       <x:c r="E459" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F459" s="38" t="str">
         <x:v>sf1</x:v>
@@ -10220,7 +10220,7 @@
         <x:v>220140</x:v>
       </x:c>
       <x:c r="E460" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F460" s="38" t="str">
         <x:v>sf2</x:v>
@@ -10241,7 +10241,7 @@
         <x:v>220141</x:v>
       </x:c>
       <x:c r="E461" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F461" s="38" t="str">
         <x:v>sw</x:v>
@@ -10262,13 +10262,13 @@
         <x:v>220142</x:v>
       </x:c>
       <x:c r="E462" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F462" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G462" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="463">
@@ -10283,7 +10283,7 @@
         <x:v>220143</x:v>
       </x:c>
       <x:c r="E463" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F463" s="38" t="str">
         <x:v>bj</x:v>
@@ -10304,7 +10304,7 @@
         <x:v>220144</x:v>
       </x:c>
       <x:c r="E464" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F464" s="38" t="str">
         <x:v>gj</x:v>
@@ -10346,7 +10346,7 @@
         <x:v>220146</x:v>
       </x:c>
       <x:c r="E466" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F466" s="38" t="str">
         <x:v>sf1</x:v>
@@ -10367,7 +10367,7 @@
         <x:v>220147</x:v>
       </x:c>
       <x:c r="E467" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F467" s="38" t="str">
         <x:v>sf2</x:v>
@@ -10388,7 +10388,7 @@
         <x:v>220148</x:v>
       </x:c>
       <x:c r="E468" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F468" s="38" t="str">
         <x:v>sw</x:v>
@@ -10409,13 +10409,13 @@
         <x:v>220149</x:v>
       </x:c>
       <x:c r="E469" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F469" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G469" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="470">
@@ -10430,7 +10430,7 @@
         <x:v>220150</x:v>
       </x:c>
       <x:c r="E470" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F470" s="38" t="str">
         <x:v>bj</x:v>
@@ -10451,7 +10451,7 @@
         <x:v>220151</x:v>
       </x:c>
       <x:c r="E471" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F471" s="38" t="str">
         <x:v>gj</x:v>
@@ -10493,7 +10493,7 @@
         <x:v>220153</x:v>
       </x:c>
       <x:c r="E473" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F473" s="38" t="str">
         <x:v>sf1</x:v>
@@ -10514,7 +10514,7 @@
         <x:v>220154</x:v>
       </x:c>
       <x:c r="E474" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F474" s="38" t="str">
         <x:v>sf2</x:v>
@@ -10535,7 +10535,7 @@
         <x:v>220155</x:v>
       </x:c>
       <x:c r="E475" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F475" s="38" t="str">
         <x:v>sw</x:v>
@@ -10556,13 +10556,13 @@
         <x:v>220156</x:v>
       </x:c>
       <x:c r="E476" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F476" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G476" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="477">
@@ -10598,13 +10598,13 @@
         <x:v>220158</x:v>
       </x:c>
       <x:c r="E478" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F478" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G478" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="479">
@@ -10619,7 +10619,7 @@
         <x:v>220159</x:v>
       </x:c>
       <x:c r="E479" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F479" s="38" t="str">
         <x:v>bj</x:v>
@@ -10640,7 +10640,7 @@
         <x:v>220160</x:v>
       </x:c>
       <x:c r="E480" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F480" s="38" t="str">
         <x:v>gj</x:v>
@@ -10682,7 +10682,7 @@
         <x:v>220162</x:v>
       </x:c>
       <x:c r="E482" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F482" s="38" t="str">
         <x:v>sf1</x:v>
@@ -10703,7 +10703,7 @@
         <x:v>220163</x:v>
       </x:c>
       <x:c r="E483" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F483" s="38" t="str">
         <x:v>sf2</x:v>
@@ -10724,7 +10724,7 @@
         <x:v>220164</x:v>
       </x:c>
       <x:c r="E484" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F484" s="38" t="str">
         <x:v>sw</x:v>
@@ -10745,13 +10745,13 @@
         <x:v>220165</x:v>
       </x:c>
       <x:c r="E485" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F485" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G485" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="486">
@@ -10766,7 +10766,7 @@
         <x:v>220166</x:v>
       </x:c>
       <x:c r="E486" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F486" s="38" t="str">
         <x:v>bj</x:v>
@@ -10787,7 +10787,7 @@
         <x:v>220167</x:v>
       </x:c>
       <x:c r="E487" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F487" s="38" t="str">
         <x:v>gj</x:v>
@@ -10829,7 +10829,7 @@
         <x:v>220169</x:v>
       </x:c>
       <x:c r="E489" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F489" s="38" t="str">
         <x:v>sf1</x:v>
@@ -10850,7 +10850,7 @@
         <x:v>220170</x:v>
       </x:c>
       <x:c r="E490" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F490" s="38" t="str">
         <x:v>sf2</x:v>
@@ -10871,7 +10871,7 @@
         <x:v>220171</x:v>
       </x:c>
       <x:c r="E491" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F491" s="38" t="str">
         <x:v>sw</x:v>
@@ -10892,13 +10892,13 @@
         <x:v>220172</x:v>
       </x:c>
       <x:c r="E492" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F492" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G492" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="493">
@@ -10913,7 +10913,7 @@
         <x:v>220173</x:v>
       </x:c>
       <x:c r="E493" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F493" s="38" t="str">
         <x:v>bj</x:v>
@@ -10934,7 +10934,7 @@
         <x:v>220174</x:v>
       </x:c>
       <x:c r="E494" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F494" s="38" t="str">
         <x:v>gj</x:v>
@@ -10976,7 +10976,7 @@
         <x:v>220176</x:v>
       </x:c>
       <x:c r="E496" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F496" s="38" t="str">
         <x:v>sf1</x:v>
@@ -10997,7 +10997,7 @@
         <x:v>220177</x:v>
       </x:c>
       <x:c r="E497" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F497" s="38" t="str">
         <x:v>sf2</x:v>
@@ -11018,7 +11018,7 @@
         <x:v>220178</x:v>
       </x:c>
       <x:c r="E498" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F498" s="38" t="str">
         <x:v>sw</x:v>
@@ -11039,13 +11039,13 @@
         <x:v>220179</x:v>
       </x:c>
       <x:c r="E499" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F499" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G499" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="500">
@@ -11060,7 +11060,7 @@
         <x:v>220180</x:v>
       </x:c>
       <x:c r="E500" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F500" s="38" t="str">
         <x:v>bj</x:v>
@@ -11081,7 +11081,7 @@
         <x:v>220181</x:v>
       </x:c>
       <x:c r="E501" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F501" s="38" t="str">
         <x:v>gj</x:v>
@@ -11123,7 +11123,7 @@
         <x:v>220183</x:v>
       </x:c>
       <x:c r="E503" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F503" s="38" t="str">
         <x:v>sf1</x:v>
@@ -11144,7 +11144,7 @@
         <x:v>220184</x:v>
       </x:c>
       <x:c r="E504" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F504" s="38" t="str">
         <x:v>sf2</x:v>
@@ -11165,7 +11165,7 @@
         <x:v>220185</x:v>
       </x:c>
       <x:c r="E505" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F505" s="38" t="str">
         <x:v>sw</x:v>
@@ -11186,13 +11186,13 @@
         <x:v>220186</x:v>
       </x:c>
       <x:c r="E506" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F506" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G506" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="507">
@@ -11207,7 +11207,7 @@
         <x:v>220187</x:v>
       </x:c>
       <x:c r="E507" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F507" s="38" t="str">
         <x:v>bj</x:v>
@@ -11228,7 +11228,7 @@
         <x:v>220188</x:v>
       </x:c>
       <x:c r="E508" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F508" s="38" t="str">
         <x:v>gj</x:v>
@@ -11270,7 +11270,7 @@
         <x:v>220190</x:v>
       </x:c>
       <x:c r="E510" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F510" s="38" t="str">
         <x:v>sf1</x:v>
@@ -11291,7 +11291,7 @@
         <x:v>220191</x:v>
       </x:c>
       <x:c r="E511" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F511" s="38" t="str">
         <x:v>sf2</x:v>
@@ -11312,7 +11312,7 @@
         <x:v>220192</x:v>
       </x:c>
       <x:c r="E512" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F512" s="38" t="str">
         <x:v>sw</x:v>
@@ -11333,13 +11333,13 @@
         <x:v>220193</x:v>
       </x:c>
       <x:c r="E513" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F513" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G513" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="514">
@@ -11354,7 +11354,7 @@
         <x:v>220194</x:v>
       </x:c>
       <x:c r="E514" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F514" s="38" t="str">
         <x:v>bj</x:v>
@@ -11375,7 +11375,7 @@
         <x:v>220195</x:v>
       </x:c>
       <x:c r="E515" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F515" s="38" t="str">
         <x:v>gj</x:v>
@@ -11417,7 +11417,7 @@
         <x:v>220197</x:v>
       </x:c>
       <x:c r="E517" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F517" s="38" t="str">
         <x:v>sf1</x:v>
@@ -11438,7 +11438,7 @@
         <x:v>220198</x:v>
       </x:c>
       <x:c r="E518" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F518" s="38" t="str">
         <x:v>sf2</x:v>
@@ -11459,7 +11459,7 @@
         <x:v>220199</x:v>
       </x:c>
       <x:c r="E519" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F519" s="38" t="str">
         <x:v>sw</x:v>
@@ -11480,13 +11480,13 @@
         <x:v>220200</x:v>
       </x:c>
       <x:c r="E520" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F520" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G520" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="521">
@@ -11501,7 +11501,7 @@
         <x:v>220201</x:v>
       </x:c>
       <x:c r="E521" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F521" s="38" t="str">
         <x:v>bj</x:v>
@@ -11522,7 +11522,7 @@
         <x:v>220202</x:v>
       </x:c>
       <x:c r="E522" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F522" s="38" t="str">
         <x:v>gj</x:v>
@@ -11564,7 +11564,7 @@
         <x:v>220204</x:v>
       </x:c>
       <x:c r="E524" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F524" s="38" t="str">
         <x:v>sf1</x:v>
@@ -11585,7 +11585,7 @@
         <x:v>220205</x:v>
       </x:c>
       <x:c r="E525" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F525" s="38" t="str">
         <x:v>sf2</x:v>
@@ -11606,7 +11606,7 @@
         <x:v>220206</x:v>
       </x:c>
       <x:c r="E526" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F526" s="38" t="str">
         <x:v>sw</x:v>
@@ -11627,13 +11627,13 @@
         <x:v>220207</x:v>
       </x:c>
       <x:c r="E527" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F527" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G527" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="528">
@@ -11648,7 +11648,7 @@
         <x:v>220208</x:v>
       </x:c>
       <x:c r="E528" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F528" s="38" t="str">
         <x:v>bj</x:v>
@@ -11669,7 +11669,7 @@
         <x:v>220209</x:v>
       </x:c>
       <x:c r="E529" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F529" s="38" t="str">
         <x:v>gj</x:v>
@@ -11711,7 +11711,7 @@
         <x:v>220211</x:v>
       </x:c>
       <x:c r="E531" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F531" s="38" t="str">
         <x:v>sf1</x:v>
@@ -11732,7 +11732,7 @@
         <x:v>220212</x:v>
       </x:c>
       <x:c r="E532" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F532" s="38" t="str">
         <x:v>sf2</x:v>
@@ -11753,7 +11753,7 @@
         <x:v>220213</x:v>
       </x:c>
       <x:c r="E533" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F533" s="38" t="str">
         <x:v>sw</x:v>
@@ -11774,13 +11774,13 @@
         <x:v>220214</x:v>
       </x:c>
       <x:c r="E534" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F534" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G534" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="535">
@@ -11795,7 +11795,7 @@
         <x:v>220215</x:v>
       </x:c>
       <x:c r="E535" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F535" s="38" t="str">
         <x:v>bj</x:v>
@@ -11816,7 +11816,7 @@
         <x:v>220216</x:v>
       </x:c>
       <x:c r="E536" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F536" s="38" t="str">
         <x:v>gj</x:v>
@@ -11858,7 +11858,7 @@
         <x:v>220218</x:v>
       </x:c>
       <x:c r="E538" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F538" s="38" t="str">
         <x:v>sf1</x:v>
@@ -11879,7 +11879,7 @@
         <x:v>220219</x:v>
       </x:c>
       <x:c r="E539" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F539" s="38" t="str">
         <x:v>sf2</x:v>
@@ -11900,7 +11900,7 @@
         <x:v>220220</x:v>
       </x:c>
       <x:c r="E540" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F540" s="38" t="str">
         <x:v>sw</x:v>
@@ -11921,13 +11921,13 @@
         <x:v>220221</x:v>
       </x:c>
       <x:c r="E541" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F541" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G541" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="542">
@@ -11942,7 +11942,7 @@
         <x:v>220222</x:v>
       </x:c>
       <x:c r="E542" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F542" s="38" t="str">
         <x:v>bj</x:v>
@@ -11963,7 +11963,7 @@
         <x:v>220223</x:v>
       </x:c>
       <x:c r="E543" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F543" s="38" t="str">
         <x:v>gj</x:v>
@@ -12005,7 +12005,7 @@
         <x:v>220225</x:v>
       </x:c>
       <x:c r="E545" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F545" s="38" t="str">
         <x:v>sf1</x:v>
@@ -12026,7 +12026,7 @@
         <x:v>220226</x:v>
       </x:c>
       <x:c r="E546" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F546" s="38" t="str">
         <x:v>sf2</x:v>
@@ -12047,7 +12047,7 @@
         <x:v>220227</x:v>
       </x:c>
       <x:c r="E547" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F547" s="38" t="str">
         <x:v>sw</x:v>
@@ -12068,13 +12068,13 @@
         <x:v>220228</x:v>
       </x:c>
       <x:c r="E548" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F548" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G548" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="549">
@@ -12089,7 +12089,7 @@
         <x:v>220229</x:v>
       </x:c>
       <x:c r="E549" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F549" s="38" t="str">
         <x:v>bj</x:v>
@@ -12110,7 +12110,7 @@
         <x:v>220230</x:v>
       </x:c>
       <x:c r="E550" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F550" s="38" t="str">
         <x:v>gj</x:v>
@@ -12152,7 +12152,7 @@
         <x:v>220232</x:v>
       </x:c>
       <x:c r="E552" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F552" s="38" t="str">
         <x:v>sf1</x:v>
@@ -12173,7 +12173,7 @@
         <x:v>220233</x:v>
       </x:c>
       <x:c r="E553" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F553" s="38" t="str">
         <x:v>sf2</x:v>
@@ -12194,7 +12194,7 @@
         <x:v>220234</x:v>
       </x:c>
       <x:c r="E554" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F554" s="38" t="str">
         <x:v>sw</x:v>
@@ -12215,13 +12215,13 @@
         <x:v>220235</x:v>
       </x:c>
       <x:c r="E555" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F555" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G555" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="556">
@@ -12236,7 +12236,7 @@
         <x:v>220236</x:v>
       </x:c>
       <x:c r="E556" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F556" s="38" t="str">
         <x:v>bj</x:v>
@@ -12257,7 +12257,7 @@
         <x:v>220237</x:v>
       </x:c>
       <x:c r="E557" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F557" s="38" t="str">
         <x:v>gj</x:v>
@@ -12299,7 +12299,7 @@
         <x:v>220239</x:v>
       </x:c>
       <x:c r="E559" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F559" s="38" t="str">
         <x:v>sf1</x:v>
@@ -12320,7 +12320,7 @@
         <x:v>220240</x:v>
       </x:c>
       <x:c r="E560" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F560" s="38" t="str">
         <x:v>sf2</x:v>
@@ -12341,7 +12341,7 @@
         <x:v>220241</x:v>
       </x:c>
       <x:c r="E561" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F561" s="38" t="str">
         <x:v>sw</x:v>
@@ -12362,13 +12362,13 @@
         <x:v>220242</x:v>
       </x:c>
       <x:c r="E562" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F562" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G562" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="563">
@@ -12383,7 +12383,7 @@
         <x:v>220243</x:v>
       </x:c>
       <x:c r="E563" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F563" s="38" t="str">
         <x:v>bj</x:v>
@@ -12404,7 +12404,7 @@
         <x:v>220244</x:v>
       </x:c>
       <x:c r="E564" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F564" s="38" t="str">
         <x:v>gj</x:v>
@@ -12446,7 +12446,7 @@
         <x:v>220246</x:v>
       </x:c>
       <x:c r="E566" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F566" s="38" t="str">
         <x:v>sf1</x:v>
@@ -12467,7 +12467,7 @@
         <x:v>220247</x:v>
       </x:c>
       <x:c r="E567" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F567" s="38" t="str">
         <x:v>sf2</x:v>
@@ -12488,7 +12488,7 @@
         <x:v>220248</x:v>
       </x:c>
       <x:c r="E568" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F568" s="38" t="str">
         <x:v>sw</x:v>
@@ -12509,13 +12509,13 @@
         <x:v>220249</x:v>
       </x:c>
       <x:c r="E569" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F569" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G569" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="570">
@@ -12530,7 +12530,7 @@
         <x:v>220250</x:v>
       </x:c>
       <x:c r="E570" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F570" s="38" t="str">
         <x:v>bj</x:v>
@@ -12551,7 +12551,7 @@
         <x:v>220251</x:v>
       </x:c>
       <x:c r="E571" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F571" s="38" t="str">
         <x:v>gj</x:v>
@@ -12593,7 +12593,7 @@
         <x:v>220253</x:v>
       </x:c>
       <x:c r="E573" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F573" s="38" t="str">
         <x:v>sf1</x:v>
@@ -12614,7 +12614,7 @@
         <x:v>220254</x:v>
       </x:c>
       <x:c r="E574" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F574" s="38" t="str">
         <x:v>sf2</x:v>
@@ -12635,7 +12635,7 @@
         <x:v>220255</x:v>
       </x:c>
       <x:c r="E575" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F575" s="38" t="str">
         <x:v>sw</x:v>
@@ -12656,13 +12656,13 @@
         <x:v>220256</x:v>
       </x:c>
       <x:c r="E576" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F576" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G576" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="577">
@@ -12677,7 +12677,7 @@
         <x:v>220257</x:v>
       </x:c>
       <x:c r="E577" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F577" s="38" t="str">
         <x:v>bj</x:v>
@@ -12698,7 +12698,7 @@
         <x:v>220258</x:v>
       </x:c>
       <x:c r="E578" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F578" s="38" t="str">
         <x:v>gj</x:v>
@@ -12740,7 +12740,7 @@
         <x:v>220260</x:v>
       </x:c>
       <x:c r="E580" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F580" s="38" t="str">
         <x:v>sf1</x:v>
@@ -12761,7 +12761,7 @@
         <x:v>220261</x:v>
       </x:c>
       <x:c r="E581" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F581" s="38" t="str">
         <x:v>sf2</x:v>
@@ -12782,7 +12782,7 @@
         <x:v>220262</x:v>
       </x:c>
       <x:c r="E582" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F582" s="38" t="str">
         <x:v>sw</x:v>
@@ -12803,13 +12803,13 @@
         <x:v>220263</x:v>
       </x:c>
       <x:c r="E583" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F583" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G583" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="584">
@@ -12824,7 +12824,7 @@
         <x:v>220264</x:v>
       </x:c>
       <x:c r="E584" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F584" s="38" t="str">
         <x:v>bj</x:v>
@@ -12845,7 +12845,7 @@
         <x:v>220265</x:v>
       </x:c>
       <x:c r="E585" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F585" s="38" t="str">
         <x:v>gj</x:v>
@@ -12887,7 +12887,7 @@
         <x:v>220267</x:v>
       </x:c>
       <x:c r="E587" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F587" s="38" t="str">
         <x:v>sf1</x:v>
@@ -12908,7 +12908,7 @@
         <x:v>220268</x:v>
       </x:c>
       <x:c r="E588" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F588" s="38" t="str">
         <x:v>sf2</x:v>
@@ -12929,7 +12929,7 @@
         <x:v>220269</x:v>
       </x:c>
       <x:c r="E589" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F589" s="38" t="str">
         <x:v>sw</x:v>
@@ -12950,13 +12950,13 @@
         <x:v>220270</x:v>
       </x:c>
       <x:c r="E590" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F590" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G590" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="591">
@@ -12971,13 +12971,13 @@
         <x:v>220271</x:v>
       </x:c>
       <x:c r="E591" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F591" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G591" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="592">
@@ -13013,7 +13013,7 @@
         <x:v>220273</x:v>
       </x:c>
       <x:c r="E593" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F593" s="38" t="str">
         <x:v>bj</x:v>
@@ -13034,7 +13034,7 @@
         <x:v>220274</x:v>
       </x:c>
       <x:c r="E594" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F594" s="38" t="str">
         <x:v>gj</x:v>
@@ -13076,7 +13076,7 @@
         <x:v>220276</x:v>
       </x:c>
       <x:c r="E596" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F596" s="38" t="str">
         <x:v>sf1</x:v>
@@ -13097,7 +13097,7 @@
         <x:v>220277</x:v>
       </x:c>
       <x:c r="E597" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F597" s="38" t="str">
         <x:v>sf2</x:v>
@@ -13118,7 +13118,7 @@
         <x:v>220278</x:v>
       </x:c>
       <x:c r="E598" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F598" s="38" t="str">
         <x:v>sw</x:v>
@@ -13139,13 +13139,13 @@
         <x:v>220279</x:v>
       </x:c>
       <x:c r="E599" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F599" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G599" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="600">
@@ -13160,7 +13160,7 @@
         <x:v>220280</x:v>
       </x:c>
       <x:c r="E600" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F600" s="38" t="str">
         <x:v>bj</x:v>
@@ -13181,7 +13181,7 @@
         <x:v>220281</x:v>
       </x:c>
       <x:c r="E601" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F601" s="38" t="str">
         <x:v>gj</x:v>
@@ -13223,7 +13223,7 @@
         <x:v>220283</x:v>
       </x:c>
       <x:c r="E603" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F603" s="38" t="str">
         <x:v>sf1</x:v>
@@ -13244,7 +13244,7 @@
         <x:v>220284</x:v>
       </x:c>
       <x:c r="E604" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F604" s="38" t="str">
         <x:v>sf2</x:v>
@@ -13265,7 +13265,7 @@
         <x:v>220285</x:v>
       </x:c>
       <x:c r="E605" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F605" s="38" t="str">
         <x:v>sw</x:v>
@@ -13286,13 +13286,13 @@
         <x:v>220286</x:v>
       </x:c>
       <x:c r="E606" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F606" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G606" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="607">
@@ -13307,7 +13307,7 @@
         <x:v>220287</x:v>
       </x:c>
       <x:c r="E607" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F607" s="38" t="str">
         <x:v>bj</x:v>
@@ -13328,7 +13328,7 @@
         <x:v>220288</x:v>
       </x:c>
       <x:c r="E608" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F608" s="38" t="str">
         <x:v>gj</x:v>
@@ -13370,7 +13370,7 @@
         <x:v>220290</x:v>
       </x:c>
       <x:c r="E610" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F610" s="38" t="str">
         <x:v>sf1</x:v>
@@ -13391,7 +13391,7 @@
         <x:v>220291</x:v>
       </x:c>
       <x:c r="E611" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F611" s="38" t="str">
         <x:v>sf2</x:v>
@@ -13412,7 +13412,7 @@
         <x:v>220292</x:v>
       </x:c>
       <x:c r="E612" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F612" s="38" t="str">
         <x:v>sw</x:v>
@@ -13433,13 +13433,13 @@
         <x:v>220293</x:v>
       </x:c>
       <x:c r="E613" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F613" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G613" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="614">
@@ -13454,7 +13454,7 @@
         <x:v>220294</x:v>
       </x:c>
       <x:c r="E614" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F614" s="38" t="str">
         <x:v>bj</x:v>
@@ -13475,7 +13475,7 @@
         <x:v>220295</x:v>
       </x:c>
       <x:c r="E615" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F615" s="38" t="str">
         <x:v>gj</x:v>
@@ -13517,7 +13517,7 @@
         <x:v>220297</x:v>
       </x:c>
       <x:c r="E617" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F617" s="38" t="str">
         <x:v>sf1</x:v>
@@ -13538,7 +13538,7 @@
         <x:v>220298</x:v>
       </x:c>
       <x:c r="E618" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F618" s="38" t="str">
         <x:v>sf2</x:v>
@@ -13559,7 +13559,7 @@
         <x:v>220299</x:v>
       </x:c>
       <x:c r="E619" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F619" s="38" t="str">
         <x:v>sw</x:v>
@@ -13580,13 +13580,13 @@
         <x:v>220300</x:v>
       </x:c>
       <x:c r="E620" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F620" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G620" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="621">
@@ -13601,7 +13601,7 @@
         <x:v>220301</x:v>
       </x:c>
       <x:c r="E621" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F621" s="38" t="str">
         <x:v>bj</x:v>
@@ -13622,7 +13622,7 @@
         <x:v>220302</x:v>
       </x:c>
       <x:c r="E622" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F622" s="38" t="str">
         <x:v>gj</x:v>
@@ -13664,7 +13664,7 @@
         <x:v>220304</x:v>
       </x:c>
       <x:c r="E624" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F624" s="38" t="str">
         <x:v>sf1</x:v>
@@ -13685,7 +13685,7 @@
         <x:v>220305</x:v>
       </x:c>
       <x:c r="E625" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F625" s="38" t="str">
         <x:v>sf2</x:v>
@@ -13706,7 +13706,7 @@
         <x:v>220306</x:v>
       </x:c>
       <x:c r="E626" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F626" s="38" t="str">
         <x:v>sw</x:v>
@@ -13727,13 +13727,13 @@
         <x:v>220307</x:v>
       </x:c>
       <x:c r="E627" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F627" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G627" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="628">
@@ -13748,7 +13748,7 @@
         <x:v>220308</x:v>
       </x:c>
       <x:c r="E628" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F628" s="38" t="str">
         <x:v>bj</x:v>
@@ -13769,7 +13769,7 @@
         <x:v>220309</x:v>
       </x:c>
       <x:c r="E629" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F629" s="38" t="str">
         <x:v>gj</x:v>
@@ -13811,7 +13811,7 @@
         <x:v>220311</x:v>
       </x:c>
       <x:c r="E631" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F631" s="38" t="str">
         <x:v>sf1</x:v>
@@ -13832,7 +13832,7 @@
         <x:v>220312</x:v>
       </x:c>
       <x:c r="E632" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F632" s="38" t="str">
         <x:v>sf2</x:v>
@@ -13853,7 +13853,7 @@
         <x:v>220313</x:v>
       </x:c>
       <x:c r="E633" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F633" s="38" t="str">
         <x:v>sw</x:v>
@@ -13874,13 +13874,13 @@
         <x:v>220314</x:v>
       </x:c>
       <x:c r="E634" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F634" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G634" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="635">
@@ -13895,7 +13895,7 @@
         <x:v>220315</x:v>
       </x:c>
       <x:c r="E635" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F635" s="38" t="str">
         <x:v>bj</x:v>
@@ -13916,7 +13916,7 @@
         <x:v>220316</x:v>
       </x:c>
       <x:c r="E636" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F636" s="38" t="str">
         <x:v>gj</x:v>
@@ -13958,7 +13958,7 @@
         <x:v>220318</x:v>
       </x:c>
       <x:c r="E638" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F638" s="38" t="str">
         <x:v>sf1</x:v>
@@ -13979,7 +13979,7 @@
         <x:v>220319</x:v>
       </x:c>
       <x:c r="E639" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F639" s="38" t="str">
         <x:v>sf2</x:v>
@@ -14000,7 +14000,7 @@
         <x:v>220320</x:v>
       </x:c>
       <x:c r="E640" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F640" s="38" t="str">
         <x:v>sw</x:v>
@@ -14021,13 +14021,13 @@
         <x:v>220321</x:v>
       </x:c>
       <x:c r="E641" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F641" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G641" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="642">
@@ -14042,7 +14042,7 @@
         <x:v>220322</x:v>
       </x:c>
       <x:c r="E642" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F642" s="38" t="str">
         <x:v>bj</x:v>
@@ -14063,7 +14063,7 @@
         <x:v>220323</x:v>
       </x:c>
       <x:c r="E643" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F643" s="38" t="str">
         <x:v>gj</x:v>
@@ -14105,7 +14105,7 @@
         <x:v>220325</x:v>
       </x:c>
       <x:c r="E645" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F645" s="38" t="str">
         <x:v>sf1</x:v>
@@ -14126,7 +14126,7 @@
         <x:v>220326</x:v>
       </x:c>
       <x:c r="E646" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F646" s="38" t="str">
         <x:v>sf2</x:v>
@@ -14147,7 +14147,7 @@
         <x:v>220327</x:v>
       </x:c>
       <x:c r="E647" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F647" s="38" t="str">
         <x:v>sw</x:v>
@@ -14168,13 +14168,13 @@
         <x:v>220328</x:v>
       </x:c>
       <x:c r="E648" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F648" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G648" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="649">
@@ -14189,7 +14189,7 @@
         <x:v>220329</x:v>
       </x:c>
       <x:c r="E649" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F649" s="38" t="str">
         <x:v>bj</x:v>
@@ -14210,7 +14210,7 @@
         <x:v>220330</x:v>
       </x:c>
       <x:c r="E650" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F650" s="38" t="str">
         <x:v>gj</x:v>
@@ -14252,7 +14252,7 @@
         <x:v>220332</x:v>
       </x:c>
       <x:c r="E652" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F652" s="38" t="str">
         <x:v>sf1</x:v>
@@ -14273,7 +14273,7 @@
         <x:v>220333</x:v>
       </x:c>
       <x:c r="E653" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F653" s="38" t="str">
         <x:v>sf2</x:v>
@@ -14294,7 +14294,7 @@
         <x:v>220334</x:v>
       </x:c>
       <x:c r="E654" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F654" s="38" t="str">
         <x:v>sw</x:v>
@@ -14315,13 +14315,13 @@
         <x:v>220335</x:v>
       </x:c>
       <x:c r="E655" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F655" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G655" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="656">
@@ -14336,7 +14336,7 @@
         <x:v>220336</x:v>
       </x:c>
       <x:c r="E656" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F656" s="38" t="str">
         <x:v>bj</x:v>
@@ -14357,7 +14357,7 @@
         <x:v>220337</x:v>
       </x:c>
       <x:c r="E657" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F657" s="38" t="str">
         <x:v>gj</x:v>
@@ -14399,7 +14399,7 @@
         <x:v>220339</x:v>
       </x:c>
       <x:c r="E659" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F659" s="38" t="str">
         <x:v>sf1</x:v>
@@ -14420,7 +14420,7 @@
         <x:v>220340</x:v>
       </x:c>
       <x:c r="E660" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F660" s="38" t="str">
         <x:v>sf2</x:v>
@@ -14441,7 +14441,7 @@
         <x:v>220341</x:v>
       </x:c>
       <x:c r="E661" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F661" s="38" t="str">
         <x:v>sw</x:v>
@@ -14462,13 +14462,13 @@
         <x:v>220342</x:v>
       </x:c>
       <x:c r="E662" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F662" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G662" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="663">
@@ -14483,7 +14483,7 @@
         <x:v>220343</x:v>
       </x:c>
       <x:c r="E663" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F663" s="38" t="str">
         <x:v>bj</x:v>
@@ -14504,7 +14504,7 @@
         <x:v>220344</x:v>
       </x:c>
       <x:c r="E664" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F664" s="38" t="str">
         <x:v>gj</x:v>
@@ -14546,7 +14546,7 @@
         <x:v>220346</x:v>
       </x:c>
       <x:c r="E666" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F666" s="38" t="str">
         <x:v>sf1</x:v>
@@ -14567,7 +14567,7 @@
         <x:v>220347</x:v>
       </x:c>
       <x:c r="E667" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F667" s="38" t="str">
         <x:v>sf2</x:v>
@@ -14588,7 +14588,7 @@
         <x:v>220348</x:v>
       </x:c>
       <x:c r="E668" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F668" s="38" t="str">
         <x:v>sw</x:v>
@@ -14609,13 +14609,13 @@
         <x:v>220349</x:v>
       </x:c>
       <x:c r="E669" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F669" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G669" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="670">
@@ -14630,7 +14630,7 @@
         <x:v>220350</x:v>
       </x:c>
       <x:c r="E670" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F670" s="38" t="str">
         <x:v>bj</x:v>
@@ -14651,7 +14651,7 @@
         <x:v>220351</x:v>
       </x:c>
       <x:c r="E671" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F671" s="38" t="str">
         <x:v>gj</x:v>
@@ -14693,7 +14693,7 @@
         <x:v>220353</x:v>
       </x:c>
       <x:c r="E673" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F673" s="38" t="str">
         <x:v>sf1</x:v>
@@ -14714,7 +14714,7 @@
         <x:v>220354</x:v>
       </x:c>
       <x:c r="E674" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F674" s="38" t="str">
         <x:v>sf2</x:v>
@@ -14735,7 +14735,7 @@
         <x:v>220355</x:v>
       </x:c>
       <x:c r="E675" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F675" s="38" t="str">
         <x:v>sw</x:v>
@@ -14756,13 +14756,13 @@
         <x:v>220356</x:v>
       </x:c>
       <x:c r="E676" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F676" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G676" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="677">
@@ -14777,7 +14777,7 @@
         <x:v>220357</x:v>
       </x:c>
       <x:c r="E677" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F677" s="38" t="str">
         <x:v>bj</x:v>
@@ -14798,7 +14798,7 @@
         <x:v>220358</x:v>
       </x:c>
       <x:c r="E678" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F678" s="38" t="str">
         <x:v>gj</x:v>
@@ -14840,7 +14840,7 @@
         <x:v>220360</x:v>
       </x:c>
       <x:c r="E680" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F680" s="38" t="str">
         <x:v>sf1</x:v>
@@ -14861,7 +14861,7 @@
         <x:v>220361</x:v>
       </x:c>
       <x:c r="E681" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F681" s="38" t="str">
         <x:v>sf2</x:v>
@@ -14882,7 +14882,7 @@
         <x:v>220362</x:v>
       </x:c>
       <x:c r="E682" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F682" s="38" t="str">
         <x:v>sw</x:v>
@@ -14903,13 +14903,13 @@
         <x:v>220363</x:v>
       </x:c>
       <x:c r="E683" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F683" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G683" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="684">
@@ -14924,7 +14924,7 @@
         <x:v>220364</x:v>
       </x:c>
       <x:c r="E684" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F684" s="38" t="str">
         <x:v>bj</x:v>
@@ -14945,7 +14945,7 @@
         <x:v>220365</x:v>
       </x:c>
       <x:c r="E685" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F685" s="38" t="str">
         <x:v>gj</x:v>
@@ -14987,7 +14987,7 @@
         <x:v>220367</x:v>
       </x:c>
       <x:c r="E687" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F687" s="38" t="str">
         <x:v>sf1</x:v>
@@ -15008,7 +15008,7 @@
         <x:v>220368</x:v>
       </x:c>
       <x:c r="E688" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F688" s="38" t="str">
         <x:v>sf2</x:v>
@@ -15029,7 +15029,7 @@
         <x:v>220369</x:v>
       </x:c>
       <x:c r="E689" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F689" s="38" t="str">
         <x:v>sw</x:v>
@@ -15050,13 +15050,13 @@
         <x:v>220370</x:v>
       </x:c>
       <x:c r="E690" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F690" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G690" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="691">
@@ -15071,7 +15071,7 @@
         <x:v>220371</x:v>
       </x:c>
       <x:c r="E691" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F691" s="38" t="str">
         <x:v>bj</x:v>
@@ -15092,7 +15092,7 @@
         <x:v>220372</x:v>
       </x:c>
       <x:c r="E692" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F692" s="38" t="str">
         <x:v>gj</x:v>
@@ -15134,7 +15134,7 @@
         <x:v>220374</x:v>
       </x:c>
       <x:c r="E694" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F694" s="38" t="str">
         <x:v>sf1</x:v>
@@ -15155,7 +15155,7 @@
         <x:v>220375</x:v>
       </x:c>
       <x:c r="E695" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F695" s="38" t="str">
         <x:v>sf2</x:v>
@@ -15176,7 +15176,7 @@
         <x:v>220376</x:v>
       </x:c>
       <x:c r="E696" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F696" s="38" t="str">
         <x:v>sw</x:v>
@@ -15197,13 +15197,13 @@
         <x:v>220377</x:v>
       </x:c>
       <x:c r="E697" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F697" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G697" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="698">
@@ -15218,7 +15218,7 @@
         <x:v>220378</x:v>
       </x:c>
       <x:c r="E698" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F698" s="38" t="str">
         <x:v>bj</x:v>
@@ -15239,7 +15239,7 @@
         <x:v>220379</x:v>
       </x:c>
       <x:c r="E699" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F699" s="38" t="str">
         <x:v>gj</x:v>
@@ -15281,7 +15281,7 @@
         <x:v>220381</x:v>
       </x:c>
       <x:c r="E701" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F701" s="38" t="str">
         <x:v>sf1</x:v>
@@ -15302,7 +15302,7 @@
         <x:v>220382</x:v>
       </x:c>
       <x:c r="E702" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F702" s="38" t="str">
         <x:v>sf2</x:v>
@@ -15323,7 +15323,7 @@
         <x:v>220383</x:v>
       </x:c>
       <x:c r="E703" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F703" s="38" t="str">
         <x:v>sw</x:v>
@@ -15344,13 +15344,13 @@
         <x:v>220384</x:v>
       </x:c>
       <x:c r="E704" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F704" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G704" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="705">
@@ -15365,7 +15365,7 @@
         <x:v>220385</x:v>
       </x:c>
       <x:c r="E705" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F705" s="38" t="str">
         <x:v>bj</x:v>
@@ -15386,7 +15386,7 @@
         <x:v>220386</x:v>
       </x:c>
       <x:c r="E706" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F706" s="38" t="str">
         <x:v>gj</x:v>
@@ -15428,7 +15428,7 @@
         <x:v>220388</x:v>
       </x:c>
       <x:c r="E708" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F708" s="38" t="str">
         <x:v>sf1</x:v>
@@ -15449,7 +15449,7 @@
         <x:v>220389</x:v>
       </x:c>
       <x:c r="E709" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F709" s="38" t="str">
         <x:v>sf2</x:v>
@@ -15470,7 +15470,7 @@
         <x:v>220390</x:v>
       </x:c>
       <x:c r="E710" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F710" s="38" t="str">
         <x:v>sw</x:v>
@@ -15491,13 +15491,13 @@
         <x:v>220391</x:v>
       </x:c>
       <x:c r="E711" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F711" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G711" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="712">
@@ -15512,7 +15512,7 @@
         <x:v>220392</x:v>
       </x:c>
       <x:c r="E712" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F712" s="38" t="str">
         <x:v>bj</x:v>
@@ -15533,7 +15533,7 @@
         <x:v>220393</x:v>
       </x:c>
       <x:c r="E713" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F713" s="38" t="str">
         <x:v>gj</x:v>
@@ -15575,7 +15575,7 @@
         <x:v>220395</x:v>
       </x:c>
       <x:c r="E715" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F715" s="38" t="str">
         <x:v>sf1</x:v>
@@ -15596,7 +15596,7 @@
         <x:v>220396</x:v>
       </x:c>
       <x:c r="E716" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F716" s="38" t="str">
         <x:v>sf2</x:v>
@@ -15617,7 +15617,7 @@
         <x:v>220397</x:v>
       </x:c>
       <x:c r="E717" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F717" s="38" t="str">
         <x:v>sw</x:v>
@@ -15638,13 +15638,13 @@
         <x:v>220398</x:v>
       </x:c>
       <x:c r="E718" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F718" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G718" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="719">
@@ -15659,7 +15659,7 @@
         <x:v>220399</x:v>
       </x:c>
       <x:c r="E719" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F719" s="38" t="str">
         <x:v>bj</x:v>
@@ -15680,7 +15680,7 @@
         <x:v>220400</x:v>
       </x:c>
       <x:c r="E720" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F720" s="38" t="str">
         <x:v>gj</x:v>
@@ -15722,7 +15722,7 @@
         <x:v>220402</x:v>
       </x:c>
       <x:c r="E722" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F722" s="38" t="str">
         <x:v>sf1</x:v>
@@ -15743,7 +15743,7 @@
         <x:v>220403</x:v>
       </x:c>
       <x:c r="E723" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F723" s="38" t="str">
         <x:v>sf2</x:v>
@@ -15764,7 +15764,7 @@
         <x:v>220404</x:v>
       </x:c>
       <x:c r="E724" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F724" s="38" t="str">
         <x:v>sw</x:v>
@@ -15785,13 +15785,13 @@
         <x:v>220405</x:v>
       </x:c>
       <x:c r="E725" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F725" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G725" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="726">
@@ -15806,7 +15806,7 @@
         <x:v>220406</x:v>
       </x:c>
       <x:c r="E726" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F726" s="38" t="str">
         <x:v>bj</x:v>
@@ -15827,7 +15827,7 @@
         <x:v>220407</x:v>
       </x:c>
       <x:c r="E727" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F727" s="38" t="str">
         <x:v>gj</x:v>
@@ -15869,7 +15869,7 @@
         <x:v>220409</x:v>
       </x:c>
       <x:c r="E729" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F729" s="38" t="str">
         <x:v>sf1</x:v>
@@ -15890,7 +15890,7 @@
         <x:v>220410</x:v>
       </x:c>
       <x:c r="E730" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F730" s="38" t="str">
         <x:v>sf2</x:v>
@@ -15911,7 +15911,7 @@
         <x:v>220411</x:v>
       </x:c>
       <x:c r="E731" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F731" s="38" t="str">
         <x:v>sw</x:v>
@@ -15932,13 +15932,13 @@
         <x:v>220412</x:v>
       </x:c>
       <x:c r="E732" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F732" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G732" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="733">
@@ -15953,7 +15953,7 @@
         <x:v>220413</x:v>
       </x:c>
       <x:c r="E733" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F733" s="38" t="str">
         <x:v>bj</x:v>
@@ -15974,7 +15974,7 @@
         <x:v>220414</x:v>
       </x:c>
       <x:c r="E734" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F734" s="38" t="str">
         <x:v>gj</x:v>
@@ -16016,7 +16016,7 @@
         <x:v>220416</x:v>
       </x:c>
       <x:c r="E736" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F736" s="38" t="str">
         <x:v>sf1</x:v>
@@ -16037,7 +16037,7 @@
         <x:v>220417</x:v>
       </x:c>
       <x:c r="E737" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F737" s="38" t="str">
         <x:v>sf2</x:v>
@@ -16058,7 +16058,7 @@
         <x:v>220418</x:v>
       </x:c>
       <x:c r="E738" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F738" s="38" t="str">
         <x:v>sw</x:v>
@@ -16079,13 +16079,13 @@
         <x:v>220419</x:v>
       </x:c>
       <x:c r="E739" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F739" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G739" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="740">
@@ -16100,7 +16100,7 @@
         <x:v>220420</x:v>
       </x:c>
       <x:c r="E740" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F740" s="38" t="str">
         <x:v>bj</x:v>
@@ -16121,7 +16121,7 @@
         <x:v>220421</x:v>
       </x:c>
       <x:c r="E741" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F741" s="38" t="str">
         <x:v>gj</x:v>
@@ -16163,7 +16163,7 @@
         <x:v>220423</x:v>
       </x:c>
       <x:c r="E743" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F743" s="38" t="str">
         <x:v>sf1</x:v>
@@ -16184,7 +16184,7 @@
         <x:v>220424</x:v>
       </x:c>
       <x:c r="E744" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F744" s="38" t="str">
         <x:v>sf2</x:v>
@@ -16205,7 +16205,7 @@
         <x:v>220425</x:v>
       </x:c>
       <x:c r="E745" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F745" s="38" t="str">
         <x:v>sw</x:v>
@@ -16226,13 +16226,13 @@
         <x:v>220426</x:v>
       </x:c>
       <x:c r="E746" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F746" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G746" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="747">
@@ -16247,7 +16247,7 @@
         <x:v>220427</x:v>
       </x:c>
       <x:c r="E747" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F747" s="38" t="str">
         <x:v>bj</x:v>
@@ -16268,7 +16268,7 @@
         <x:v>220428</x:v>
       </x:c>
       <x:c r="E748" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F748" s="38" t="str">
         <x:v>gj</x:v>
@@ -16310,7 +16310,7 @@
         <x:v>220430</x:v>
       </x:c>
       <x:c r="E750" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F750" s="38" t="str">
         <x:v>sf1</x:v>
@@ -16331,7 +16331,7 @@
         <x:v>220431</x:v>
       </x:c>
       <x:c r="E751" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F751" s="38" t="str">
         <x:v>sf2</x:v>
@@ -16352,7 +16352,7 @@
         <x:v>220432</x:v>
       </x:c>
       <x:c r="E752" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F752" s="38" t="str">
         <x:v>sw</x:v>
@@ -16373,13 +16373,13 @@
         <x:v>220433</x:v>
       </x:c>
       <x:c r="E753" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F753" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G753" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="754">
@@ -16394,7 +16394,7 @@
         <x:v>220434</x:v>
       </x:c>
       <x:c r="E754" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F754" s="38" t="str">
         <x:v>bj</x:v>
@@ -16415,7 +16415,7 @@
         <x:v>220435</x:v>
       </x:c>
       <x:c r="E755" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F755" s="38" t="str">
         <x:v>gj</x:v>
@@ -16457,7 +16457,7 @@
         <x:v>220437</x:v>
       </x:c>
       <x:c r="E757" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F757" s="38" t="str">
         <x:v>sf1</x:v>
@@ -16478,7 +16478,7 @@
         <x:v>220438</x:v>
       </x:c>
       <x:c r="E758" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F758" s="38" t="str">
         <x:v>sf2</x:v>
@@ -16499,7 +16499,7 @@
         <x:v>220439</x:v>
       </x:c>
       <x:c r="E759" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F759" s="38" t="str">
         <x:v>sw</x:v>
@@ -16520,13 +16520,13 @@
         <x:v>220440</x:v>
       </x:c>
       <x:c r="E760" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F760" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G760" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="761">
@@ -16541,7 +16541,7 @@
         <x:v>220441</x:v>
       </x:c>
       <x:c r="E761" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F761" s="38" t="str">
         <x:v>bj</x:v>
@@ -16562,7 +16562,7 @@
         <x:v>220442</x:v>
       </x:c>
       <x:c r="E762" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F762" s="38" t="str">
         <x:v>gj</x:v>
@@ -16604,7 +16604,7 @@
         <x:v>220444</x:v>
       </x:c>
       <x:c r="E764" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F764" s="38" t="str">
         <x:v>sf1</x:v>
@@ -16625,7 +16625,7 @@
         <x:v>220445</x:v>
       </x:c>
       <x:c r="E765" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F765" s="38" t="str">
         <x:v>sf2</x:v>
@@ -16646,7 +16646,7 @@
         <x:v>220446</x:v>
       </x:c>
       <x:c r="E766" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F766" s="38" t="str">
         <x:v>sw</x:v>
@@ -16667,13 +16667,13 @@
         <x:v>220447</x:v>
       </x:c>
       <x:c r="E767" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F767" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G767" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="768">
@@ -16688,7 +16688,7 @@
         <x:v>220448</x:v>
       </x:c>
       <x:c r="E768" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F768" s="38" t="str">
         <x:v>bj</x:v>
@@ -16709,7 +16709,7 @@
         <x:v>220449</x:v>
       </x:c>
       <x:c r="E769" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F769" s="38" t="str">
         <x:v>gj</x:v>
@@ -16751,7 +16751,7 @@
         <x:v>220451</x:v>
       </x:c>
       <x:c r="E771" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F771" s="38" t="str">
         <x:v>sf1</x:v>
@@ -16772,7 +16772,7 @@
         <x:v>220452</x:v>
       </x:c>
       <x:c r="E772" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F772" s="38" t="str">
         <x:v>sf2</x:v>
@@ -16793,7 +16793,7 @@
         <x:v>220453</x:v>
       </x:c>
       <x:c r="E773" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F773" s="38" t="str">
         <x:v>sw</x:v>
@@ -16814,13 +16814,13 @@
         <x:v>220454</x:v>
       </x:c>
       <x:c r="E774" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F774" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G774" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="775">
@@ -16835,7 +16835,7 @@
         <x:v>220455</x:v>
       </x:c>
       <x:c r="E775" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F775" s="38" t="str">
         <x:v>bj</x:v>
@@ -16856,7 +16856,7 @@
         <x:v>220456</x:v>
       </x:c>
       <x:c r="E776" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F776" s="38" t="str">
         <x:v>gj</x:v>
@@ -16898,7 +16898,7 @@
         <x:v>220458</x:v>
       </x:c>
       <x:c r="E778" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F778" s="38" t="str">
         <x:v>sf1</x:v>
@@ -16919,7 +16919,7 @@
         <x:v>220459</x:v>
       </x:c>
       <x:c r="E779" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F779" s="38" t="str">
         <x:v>sf2</x:v>
@@ -16940,7 +16940,7 @@
         <x:v>220460</x:v>
       </x:c>
       <x:c r="E780" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F780" s="38" t="str">
         <x:v>sw</x:v>
@@ -16961,13 +16961,13 @@
         <x:v>220461</x:v>
       </x:c>
       <x:c r="E781" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F781" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G781" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="782">
@@ -16982,7 +16982,7 @@
         <x:v>220462</x:v>
       </x:c>
       <x:c r="E782" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F782" s="38" t="str">
         <x:v>bj</x:v>
@@ -17003,7 +17003,7 @@
         <x:v>220463</x:v>
       </x:c>
       <x:c r="E783" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F783" s="38" t="str">
         <x:v>gj</x:v>
@@ -17045,7 +17045,7 @@
         <x:v>220465</x:v>
       </x:c>
       <x:c r="E785" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F785" s="38" t="str">
         <x:v>sf1</x:v>
@@ -17066,7 +17066,7 @@
         <x:v>220466</x:v>
       </x:c>
       <x:c r="E786" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F786" s="38" t="str">
         <x:v>sf2</x:v>
@@ -17087,7 +17087,7 @@
         <x:v>220467</x:v>
       </x:c>
       <x:c r="E787" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F787" s="38" t="str">
         <x:v>sw</x:v>
@@ -17108,13 +17108,13 @@
         <x:v>220468</x:v>
       </x:c>
       <x:c r="E788" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F788" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G788" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="789">
@@ -17129,7 +17129,7 @@
         <x:v>220469</x:v>
       </x:c>
       <x:c r="E789" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F789" s="38" t="str">
         <x:v>bj</x:v>
@@ -17150,7 +17150,7 @@
         <x:v>220470</x:v>
       </x:c>
       <x:c r="E790" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F790" s="38" t="str">
         <x:v>gj</x:v>
@@ -17192,7 +17192,7 @@
         <x:v>220472</x:v>
       </x:c>
       <x:c r="E792" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F792" s="38" t="str">
         <x:v>sf1</x:v>
@@ -17213,7 +17213,7 @@
         <x:v>220473</x:v>
       </x:c>
       <x:c r="E793" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F793" s="38" t="str">
         <x:v>sf2</x:v>
@@ -17234,7 +17234,7 @@
         <x:v>220474</x:v>
       </x:c>
       <x:c r="E794" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F794" s="38" t="str">
         <x:v>sw</x:v>
@@ -17255,13 +17255,13 @@
         <x:v>220475</x:v>
       </x:c>
       <x:c r="E795" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F795" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G795" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="796">
@@ -17276,7 +17276,7 @@
         <x:v>220476</x:v>
       </x:c>
       <x:c r="E796" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F796" s="38" t="str">
         <x:v>bj</x:v>
@@ -17297,7 +17297,7 @@
         <x:v>220477</x:v>
       </x:c>
       <x:c r="E797" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F797" s="38" t="str">
         <x:v>gj</x:v>
@@ -17339,7 +17339,7 @@
         <x:v>220479</x:v>
       </x:c>
       <x:c r="E799" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F799" s="38" t="str">
         <x:v>sf1</x:v>
@@ -17360,7 +17360,7 @@
         <x:v>220480</x:v>
       </x:c>
       <x:c r="E800" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F800" s="38" t="str">
         <x:v>sf2</x:v>
@@ -17381,7 +17381,7 @@
         <x:v>220481</x:v>
       </x:c>
       <x:c r="E801" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F801" s="38" t="str">
         <x:v>sw</x:v>
@@ -17402,13 +17402,13 @@
         <x:v>220482</x:v>
       </x:c>
       <x:c r="E802" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F802" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G802" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="803">
@@ -17423,7 +17423,7 @@
         <x:v>220483</x:v>
       </x:c>
       <x:c r="E803" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F803" s="38" t="str">
         <x:v>bj</x:v>
@@ -17444,7 +17444,7 @@
         <x:v>220484</x:v>
       </x:c>
       <x:c r="E804" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F804" s="38" t="str">
         <x:v>gj</x:v>
@@ -17486,7 +17486,7 @@
         <x:v>220486</x:v>
       </x:c>
       <x:c r="E806" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F806" s="38" t="str">
         <x:v>sf1</x:v>
@@ -17507,7 +17507,7 @@
         <x:v>220487</x:v>
       </x:c>
       <x:c r="E807" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F807" s="38" t="str">
         <x:v>sf2</x:v>
@@ -17528,7 +17528,7 @@
         <x:v>220488</x:v>
       </x:c>
       <x:c r="E808" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F808" s="38" t="str">
         <x:v>sw</x:v>
@@ -17549,13 +17549,13 @@
         <x:v>220489</x:v>
       </x:c>
       <x:c r="E809" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F809" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G809" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="810">
@@ -17570,13 +17570,13 @@
         <x:v>220490</x:v>
       </x:c>
       <x:c r="E810" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F810" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G810" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="811">
@@ -17591,7 +17591,7 @@
         <x:v>220491</x:v>
       </x:c>
       <x:c r="E811" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F811" s="38" t="str">
         <x:v>bj</x:v>
@@ -17612,7 +17612,7 @@
         <x:v>220492</x:v>
       </x:c>
       <x:c r="E812" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F812" s="38" t="str">
         <x:v>gj</x:v>
@@ -17654,7 +17654,7 @@
         <x:v>220494</x:v>
       </x:c>
       <x:c r="E814" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F814" s="38" t="str">
         <x:v>sf1</x:v>
@@ -17675,7 +17675,7 @@
         <x:v>220495</x:v>
       </x:c>
       <x:c r="E815" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F815" s="38" t="str">
         <x:v>sf2</x:v>
@@ -17696,7 +17696,7 @@
         <x:v>220496</x:v>
       </x:c>
       <x:c r="E816" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F816" s="38" t="str">
         <x:v>sw</x:v>
@@ -17717,13 +17717,13 @@
         <x:v>220497</x:v>
       </x:c>
       <x:c r="E817" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F817" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G817" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="818">
@@ -17738,7 +17738,7 @@
         <x:v>220498</x:v>
       </x:c>
       <x:c r="E818" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F818" s="38" t="str">
         <x:v>bj</x:v>
@@ -17759,7 +17759,7 @@
         <x:v>220499</x:v>
       </x:c>
       <x:c r="E819" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F819" s="38" t="str">
         <x:v>gj</x:v>
@@ -17801,7 +17801,7 @@
         <x:v>220501</x:v>
       </x:c>
       <x:c r="E821" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F821" s="38" t="str">
         <x:v>sf1</x:v>
@@ -17822,7 +17822,7 @@
         <x:v>220502</x:v>
       </x:c>
       <x:c r="E822" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F822" s="38" t="str">
         <x:v>sf2</x:v>
@@ -17843,7 +17843,7 @@
         <x:v>220503</x:v>
       </x:c>
       <x:c r="E823" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F823" s="38" t="str">
         <x:v>sw</x:v>
@@ -17864,13 +17864,13 @@
         <x:v>220504</x:v>
       </x:c>
       <x:c r="E824" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F824" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G824" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="825">
@@ -17885,7 +17885,7 @@
         <x:v>220505</x:v>
       </x:c>
       <x:c r="E825" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F825" s="38" t="str">
         <x:v>bj</x:v>
@@ -17906,7 +17906,7 @@
         <x:v>220506</x:v>
       </x:c>
       <x:c r="E826" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F826" s="38" t="str">
         <x:v>gj</x:v>
@@ -17948,7 +17948,7 @@
         <x:v>220508</x:v>
       </x:c>
       <x:c r="E828" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F828" s="38" t="str">
         <x:v>sf1</x:v>
@@ -17969,7 +17969,7 @@
         <x:v>220509</x:v>
       </x:c>
       <x:c r="E829" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="F829" s="38" t="str">
         <x:v>sf2</x:v>
@@ -17990,7 +17990,7 @@
         <x:v>220510</x:v>
       </x:c>
       <x:c r="E830" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Death</x:v>
       </x:c>
       <x:c r="F830" s="38" t="str">
         <x:v>sw</x:v>
@@ -18011,13 +18011,13 @@
         <x:v>220511</x:v>
       </x:c>
       <x:c r="E831" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F831" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G831" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="832">
@@ -18032,13 +18032,13 @@
         <x:v>220512</x:v>
       </x:c>
       <x:c r="E832" s="38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Stand</x:v>
       </x:c>
       <x:c r="F832" s="38" t="str">
         <x:v>zd</x:v>
       </x:c>
       <x:c r="G832" s="39" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="833">
